--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
@@ -3077,7 +3077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD57"/>
+  <dimension ref="A1:AE57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3147,7 +3147,8 @@
       <c r="AA1" s="74" t="n"/>
       <c r="AB1" s="74" t="n"/>
       <c r="AC1" s="74" t="n"/>
-      <c r="AD1" s="75" t="n"/>
+      <c r="AD1" s="74" t="n"/>
+      <c r="AE1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="105" t="inlineStr">
@@ -3182,12 +3183,8 @@
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="74" t="n"/>
       <c r="AB2" s="74" t="n"/>
-      <c r="AC2" s="75" t="n"/>
-      <c r="AD2" s="106" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:42</t>
-        </is>
-      </c>
+      <c r="AC2" s="74" t="n"/>
+      <c r="AD2" s="75" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">
@@ -3575,7 +3572,7 @@
         <v>0.009166666666666667</v>
       </c>
       <c r="T5" s="58" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U5" s="50" t="inlineStr">
         <is>
@@ -3675,7 +3672,7 @@
         <v>0.007800000000000001</v>
       </c>
       <c r="T6" s="67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U6" s="59" t="inlineStr">
         <is>
@@ -3769,7 +3766,7 @@
       <c r="R7" s="51" t="n"/>
       <c r="S7" s="57" t="n"/>
       <c r="T7" s="58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U7" s="50" t="inlineStr">
         <is>
@@ -3867,7 +3864,7 @@
       <c r="R8" s="60" t="n"/>
       <c r="S8" s="59" t="n"/>
       <c r="T8" s="67" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="U8" s="59" t="inlineStr">
         <is>
@@ -3965,7 +3962,7 @@
       <c r="R9" s="51" t="n"/>
       <c r="S9" s="57" t="n"/>
       <c r="T9" s="58" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="U9" s="50" t="inlineStr">
         <is>
@@ -4059,7 +4056,7 @@
       <c r="R10" s="60" t="n"/>
       <c r="S10" s="59" t="n"/>
       <c r="T10" s="67" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="U10" s="59" t="inlineStr">
         <is>
@@ -4153,7 +4150,7 @@
       <c r="R11" s="51" t="n"/>
       <c r="S11" s="57" t="n"/>
       <c r="T11" s="58" t="n">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="U11" s="50" t="inlineStr">
         <is>
@@ -4247,7 +4244,7 @@
       <c r="R12" s="60" t="n"/>
       <c r="S12" s="66" t="n"/>
       <c r="T12" s="67" t="n">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="U12" s="59" t="inlineStr">
         <is>
@@ -4341,7 +4338,7 @@
       <c r="R13" s="51" t="n"/>
       <c r="S13" s="50" t="n"/>
       <c r="T13" s="58" t="n">
-        <v>-38</v>
+        <v>-37</v>
       </c>
       <c r="U13" s="50" t="inlineStr">
         <is>
@@ -4435,7 +4432,7 @@
       <c r="R14" s="60" t="n"/>
       <c r="S14" s="66" t="n"/>
       <c r="T14" s="67" t="n">
-        <v>-87</v>
+        <v>-86</v>
       </c>
       <c r="U14" s="59" t="inlineStr">
         <is>
@@ -4529,7 +4526,7 @@
       <c r="R15" s="51" t="n"/>
       <c r="S15" s="50" t="n"/>
       <c r="T15" s="58" t="n">
-        <v>-87</v>
+        <v>-86</v>
       </c>
       <c r="U15" s="50" t="inlineStr">
         <is>
@@ -11701,7 +11698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD41"/>
+  <dimension ref="A1:AE41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11771,7 +11768,8 @@
       <c r="AA1" s="74" t="n"/>
       <c r="AB1" s="74" t="n"/>
       <c r="AC1" s="74" t="n"/>
-      <c r="AD1" s="75" t="n"/>
+      <c r="AD1" s="74" t="n"/>
+      <c r="AE1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="105" t="inlineStr">
@@ -11806,12 +11804,8 @@
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="74" t="n"/>
       <c r="AB2" s="74" t="n"/>
-      <c r="AC2" s="75" t="n"/>
-      <c r="AD2" s="106" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:42</t>
-        </is>
-      </c>
+      <c r="AC2" s="74" t="n"/>
+      <c r="AD2" s="75" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">
@@ -15551,7 +15545,7 @@
       </c>
       <c r="F5" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G5" s="50" t="inlineStr">
@@ -15586,7 +15580,7 @@
       </c>
       <c r="F6" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G6" s="59" t="inlineStr">
@@ -15621,7 +15615,7 @@
       </c>
       <c r="F7" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G7" s="50" t="inlineStr">
@@ -15656,7 +15650,7 @@
       </c>
       <c r="F8" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G8" s="59" t="inlineStr">
@@ -15691,7 +15685,7 @@
       </c>
       <c r="F9" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G9" s="50" t="inlineStr">
@@ -15726,7 +15720,7 @@
       </c>
       <c r="F10" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G10" s="59" t="inlineStr">
@@ -15761,7 +15755,7 @@
       </c>
       <c r="F11" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G11" s="50" t="inlineStr">
@@ -15796,7 +15790,7 @@
       </c>
       <c r="F12" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G12" s="59" t="inlineStr">
@@ -15831,7 +15825,7 @@
       </c>
       <c r="F13" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G13" s="50" t="inlineStr">
@@ -15866,7 +15860,7 @@
       </c>
       <c r="F14" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G14" s="59" t="inlineStr">
@@ -15901,7 +15895,7 @@
       </c>
       <c r="F15" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G15" s="50" t="inlineStr">
@@ -15936,7 +15930,7 @@
       </c>
       <c r="F16" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G16" s="59" t="inlineStr">
@@ -15971,7 +15965,7 @@
       </c>
       <c r="F17" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G17" s="50" t="inlineStr">
@@ -16006,7 +16000,7 @@
       </c>
       <c r="F18" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G18" s="59" t="inlineStr">
@@ -16041,7 +16035,7 @@
       </c>
       <c r="F19" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G19" s="50" t="inlineStr">
@@ -16076,7 +16070,7 @@
       </c>
       <c r="F20" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G20" s="59" t="inlineStr">
@@ -16111,7 +16105,7 @@
       </c>
       <c r="F21" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G21" s="50" t="inlineStr">
@@ -16146,7 +16140,7 @@
       </c>
       <c r="F22" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G22" s="59" t="inlineStr">
@@ -16181,7 +16175,7 @@
       </c>
       <c r="F23" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G23" s="50" t="inlineStr">
@@ -16216,7 +16210,7 @@
       </c>
       <c r="F24" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G24" s="59" t="inlineStr">
@@ -16251,7 +16245,7 @@
       </c>
       <c r="F25" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G25" s="50" t="inlineStr">
@@ -16286,7 +16280,7 @@
       </c>
       <c r="F26" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G26" s="59" t="inlineStr">
@@ -16321,7 +16315,7 @@
       </c>
       <c r="F27" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G27" s="50" t="inlineStr">
@@ -16810,7 +16804,7 @@
       </c>
       <c r="F5" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -16840,7 +16834,7 @@
       </c>
       <c r="F6" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -16870,7 +16864,7 @@
       </c>
       <c r="F7" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -16900,7 +16894,7 @@
       </c>
       <c r="F8" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -16930,7 +16924,7 @@
       </c>
       <c r="F9" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -16960,7 +16954,7 @@
       </c>
       <c r="F10" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -16990,7 +16984,7 @@
       </c>
       <c r="F11" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -17020,7 +17014,7 @@
       </c>
       <c r="F12" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -17050,7 +17044,7 @@
       </c>
       <c r="F13" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -17080,7 +17074,7 @@
       </c>
       <c r="F14" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -17110,7 +17104,7 @@
       </c>
       <c r="F15" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -17140,7 +17134,7 @@
       </c>
       <c r="F16" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -17170,7 +17164,7 @@
       </c>
       <c r="F17" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -17200,7 +17194,7 @@
       </c>
       <c r="F18" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17224,7 @@
       </c>
       <c r="F19" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -17260,7 +17254,7 @@
       </c>
       <c r="F20" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -17290,7 +17284,7 @@
       </c>
       <c r="F21" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -17320,7 +17314,7 @@
       </c>
       <c r="F22" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -17350,7 +17344,7 @@
       </c>
       <c r="F23" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -17380,7 +17374,7 @@
       </c>
       <c r="F24" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17404,7 @@
       </c>
       <c r="F25" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -17440,7 +17434,7 @@
       </c>
       <c r="F26" s="59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -17470,7 +17464,7 @@
       </c>
       <c r="F27" s="50" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
     </row>
@@ -17787,7 +17781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD34"/>
+  <dimension ref="A1:AE34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -17857,7 +17851,8 @@
       <c r="AA1" s="74" t="n"/>
       <c r="AB1" s="74" t="n"/>
       <c r="AC1" s="74" t="n"/>
-      <c r="AD1" s="75" t="n"/>
+      <c r="AD1" s="74" t="n"/>
+      <c r="AE1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="105" t="inlineStr">
@@ -17892,12 +17887,8 @@
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="74" t="n"/>
       <c r="AB2" s="74" t="n"/>
-      <c r="AC2" s="75" t="n"/>
-      <c r="AD2" s="106" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:42</t>
-        </is>
-      </c>
+      <c r="AC2" s="74" t="n"/>
+      <c r="AD2" s="75" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">
@@ -19237,7 +19228,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="109" t="inlineStr">
         <is>
-          <t>㈜케이엔케이 │ 관리코드 일관성 불일치 보고 │ 2026-05-02</t>
+          <t>㈜케이엔케이 │ 관리코드 일관성 불일치 보고 │ 2026-05-03</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
@@ -438,7 +438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
@@ -800,6 +800,15 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="29" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1623,46 +1632,42 @@
     </comment>
     <comment ref="AJ4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+  1) '제외' 선택 → 베트남 미참여
+  2) 빈 칸 → 베트남 참여 확정, 담당자 미정
+  3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
+• 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
       </text>
     </comment>
     <comment ref="AK4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+  1) '제외' 선택 → 베트남 미참여
+  2) 빈 칸 → 베트남 참여 확정, 담당자 미정
+  3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
+• 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
       </text>
     </comment>
     <comment ref="AL4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+  1) '제외' 선택 → 베트남 미참여
+  2) 빈 칸 → 베트남 참여 확정, 담당자 미정
+  3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
+• 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
       </text>
     </comment>
     <comment ref="AM4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
-  1) '제외' 선택 → 이 부서 미참여
-     (해당 부서 파일에 프로젝트 안 올라감)
-  2) 빈 칸 → 부서 참여 확정, 담당자 미정
-  3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
-• 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+  1) '제외' 선택 → 베트남 미참여
+  2) 빈 칸 → 베트남 참여 확정, 담당자 미정
+  3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
+• 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
       </text>
     </comment>
     <comment ref="AN4" authorId="0" shapeId="0">
@@ -3077,7 +3082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE57"/>
+  <dimension ref="A1:AD57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3106,15 +3111,15 @@
     <col width="12" customWidth="1" style="97" min="24" max="24"/>
     <col width="14" customWidth="1" style="97" min="25" max="25"/>
     <col width="8" customWidth="1" style="97" min="26" max="27"/>
-    <col width="8" customWidth="1" style="97" min="27" max="27"/>
-    <col width="13" customWidth="1" style="97" min="28" max="28"/>
-    <col width="8" customWidth="1" style="97" min="29" max="29"/>
+    <col width="13" customWidth="1" style="97" min="27" max="27"/>
+    <col width="8" customWidth="1" style="97" min="28" max="28"/>
+    <col width="12" customWidth="1" style="97" min="29" max="29"/>
     <col width="12" customWidth="1" style="97" min="30" max="30"/>
     <col width="12" customWidth="1" style="97" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="104" t="inlineStr">
+      <c r="A1" s="116" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -3147,11 +3152,10 @@
       <c r="AA1" s="74" t="n"/>
       <c r="AB1" s="74" t="n"/>
       <c r="AC1" s="74" t="n"/>
-      <c r="AD1" s="74" t="n"/>
-      <c r="AE1" s="75" t="n"/>
+      <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="105" t="inlineStr">
+      <c r="A2" s="117" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -3183,8 +3187,12 @@
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="74" t="n"/>
       <c r="AB2" s="74" t="n"/>
-      <c r="AC2" s="74" t="n"/>
-      <c r="AD2" s="75" t="n"/>
+      <c r="AC2" s="75" t="n"/>
+      <c r="AD2" s="118" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:44</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">
@@ -3554,7 +3562,7 @@
       <c r="N5" s="54" t="n">
         <v>56900000</v>
       </c>
-      <c r="O5" s="78" t="n">
+      <c r="O5" s="55" t="n">
         <v>227600000</v>
       </c>
       <c r="P5" s="56" t="inlineStr">
@@ -3654,7 +3662,7 @@
       <c r="N6" s="63" t="n">
         <v>75840000</v>
       </c>
-      <c r="O6" s="79" t="n">
+      <c r="O6" s="64" t="n">
         <v>75840000</v>
       </c>
       <c r="P6" s="65" t="inlineStr">
@@ -3750,7 +3758,7 @@
       <c r="N7" s="54" t="n">
         <v>230700000</v>
       </c>
-      <c r="O7" s="78" t="n">
+      <c r="O7" s="55" t="n">
         <v>1614900000</v>
       </c>
       <c r="P7" s="56" t="inlineStr">
@@ -3848,7 +3856,7 @@
       <c r="N8" s="63" t="n">
         <v>230700000</v>
       </c>
-      <c r="O8" s="79" t="n">
+      <c r="O8" s="64" t="n">
         <v>1614900000</v>
       </c>
       <c r="P8" s="65" t="inlineStr">
@@ -3946,7 +3954,7 @@
       <c r="N9" s="54" t="n">
         <v>26000000</v>
       </c>
-      <c r="O9" s="78" t="n">
+      <c r="O9" s="55" t="n">
         <v>104000000</v>
       </c>
       <c r="P9" s="56" t="inlineStr">
@@ -4040,7 +4048,7 @@
       <c r="N10" s="63" t="n">
         <v>230700000</v>
       </c>
-      <c r="O10" s="79" t="n">
+      <c r="O10" s="64" t="n">
         <v>1845600000</v>
       </c>
       <c r="P10" s="65" t="inlineStr">
@@ -4134,7 +4142,7 @@
       <c r="N11" s="54" t="n">
         <v>254500000</v>
       </c>
-      <c r="O11" s="78" t="n">
+      <c r="O11" s="55" t="n">
         <v>254500000</v>
       </c>
       <c r="P11" s="56" t="inlineStr">
@@ -4228,7 +4236,7 @@
       <c r="N12" s="63" t="n">
         <v>227700000</v>
       </c>
-      <c r="O12" s="79" t="n">
+      <c r="O12" s="64" t="n">
         <v>1138500000</v>
       </c>
       <c r="P12" s="65" t="inlineStr">
@@ -4322,7 +4330,7 @@
       <c r="N13" s="54" t="n">
         <v>230700000</v>
       </c>
-      <c r="O13" s="78" t="n">
+      <c r="O13" s="55" t="n">
         <v>1384200000</v>
       </c>
       <c r="P13" s="56" t="inlineStr">
@@ -4416,7 +4424,7 @@
       <c r="N14" s="63" t="n">
         <v>248900000</v>
       </c>
-      <c r="O14" s="79" t="n">
+      <c r="O14" s="64" t="n">
         <v>995600000</v>
       </c>
       <c r="P14" s="65" t="inlineStr">
@@ -4510,7 +4518,7 @@
       <c r="N15" s="54" t="n">
         <v>248900000</v>
       </c>
-      <c r="O15" s="78" t="n">
+      <c r="O15" s="55" t="n">
         <v>746700000</v>
       </c>
       <c r="P15" s="56" t="inlineStr">
@@ -4604,7 +4612,7 @@
       <c r="N16" s="63" t="n">
         <v>65810000</v>
       </c>
-      <c r="O16" s="79" t="n">
+      <c r="O16" s="64" t="n">
         <v>131620000</v>
       </c>
       <c r="P16" s="65" t="inlineStr">
@@ -4702,7 +4710,7 @@
       <c r="N17" s="54" t="n">
         <v>59750000</v>
       </c>
-      <c r="O17" s="78" t="n">
+      <c r="O17" s="55" t="n">
         <v>119500000</v>
       </c>
       <c r="P17" s="56" t="inlineStr">
@@ -4800,7 +4808,7 @@
       <c r="N18" s="63" t="n">
         <v>59290000</v>
       </c>
-      <c r="O18" s="79" t="n">
+      <c r="O18" s="64" t="n">
         <v>59290000</v>
       </c>
       <c r="P18" s="65" t="inlineStr">
@@ -4892,7 +4900,7 @@
       <c r="N19" s="54" t="n">
         <v>26000000</v>
       </c>
-      <c r="O19" s="78" t="n">
+      <c r="O19" s="55" t="n">
         <v>26000000</v>
       </c>
       <c r="P19" s="56" t="inlineStr">
@@ -4984,7 +4992,7 @@
       <c r="N20" s="63" t="n">
         <v>28000000</v>
       </c>
-      <c r="O20" s="79" t="n">
+      <c r="O20" s="64" t="n">
         <v>28000000</v>
       </c>
       <c r="P20" s="65" t="inlineStr">
@@ -5076,7 +5084,7 @@
       <c r="N21" s="54" t="n">
         <v>36010000</v>
       </c>
-      <c r="O21" s="78" t="n">
+      <c r="O21" s="55" t="n">
         <v>36010000</v>
       </c>
       <c r="P21" s="56" t="inlineStr">
@@ -5127,12 +5135,12 @@
         </is>
       </c>
       <c r="E22" s="60" t="n"/>
-      <c r="F22" s="108" t="inlineStr">
+      <c r="F22" s="61" t="inlineStr">
         <is>
           <t>Display 압착 자동화설비</t>
         </is>
       </c>
-      <c r="G22" s="108" t="inlineStr">
+      <c r="G22" s="61" t="inlineStr">
         <is>
           <t>BATTPRESSAUTO-S-V2</t>
         </is>
@@ -5168,7 +5176,7 @@
       <c r="N22" s="63" t="n">
         <v>25779</v>
       </c>
-      <c r="O22" s="79" t="n">
+      <c r="O22" s="64" t="n">
         <v>232011</v>
       </c>
       <c r="P22" s="65" t="inlineStr">
@@ -5219,12 +5227,12 @@
         </is>
       </c>
       <c r="E23" s="51" t="n"/>
-      <c r="F23" s="107" t="inlineStr">
+      <c r="F23" s="52" t="inlineStr">
         <is>
           <t>지문센서조립 자동화 설비</t>
         </is>
       </c>
-      <c r="G23" s="107" t="inlineStr">
+      <c r="G23" s="52" t="inlineStr">
         <is>
           <t>FINGERASSY-S-V1</t>
         </is>
@@ -5260,7 +5268,7 @@
       <c r="N23" s="54" t="n">
         <v>49055</v>
       </c>
-      <c r="O23" s="78" t="n">
+      <c r="O23" s="55" t="n">
         <v>196220</v>
       </c>
       <c r="P23" s="56" t="inlineStr">
@@ -5311,12 +5319,12 @@
         </is>
       </c>
       <c r="E24" s="60" t="n"/>
-      <c r="F24" s="107" t="inlineStr">
+      <c r="F24" s="61" t="inlineStr">
         <is>
           <t>지문센서조립 자동화 설비</t>
         </is>
       </c>
-      <c r="G24" s="107" t="inlineStr">
+      <c r="G24" s="61" t="inlineStr">
         <is>
           <t>지문센서 조립기 변위 센서 IL-100, IL-1000, OP-87056, 개조품DL-RS1A, 가공품</t>
         </is>
@@ -5352,7 +5360,7 @@
       <c r="N24" s="63" t="n">
         <v>1480000</v>
       </c>
-      <c r="O24" s="79" t="n">
+      <c r="O24" s="64" t="n">
         <v>7400000</v>
       </c>
       <c r="P24" s="65" t="inlineStr">
@@ -5444,7 +5452,7 @@
       <c r="N25" s="54" t="n">
         <v>241900000</v>
       </c>
-      <c r="O25" s="78" t="n">
+      <c r="O25" s="55" t="n">
         <v>241900000</v>
       </c>
       <c r="P25" s="56" t="inlineStr">
@@ -5536,7 +5544,7 @@
       <c r="N26" s="63" t="n">
         <v>241900000</v>
       </c>
-      <c r="O26" s="79" t="n">
+      <c r="O26" s="64" t="n">
         <v>2902800000</v>
       </c>
       <c r="P26" s="65" t="inlineStr">
@@ -5628,7 +5636,7 @@
       <c r="N27" s="54" t="n">
         <v>98000000</v>
       </c>
-      <c r="O27" s="78" t="n">
+      <c r="O27" s="55" t="n">
         <v>98000000</v>
       </c>
       <c r="P27" s="56" t="inlineStr">
@@ -6622,10 +6630,10 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:AE1"/>
-    <mergeCell ref="A2:AD2"/>
+    <mergeCell ref="A2:AC2"/>
+    <mergeCell ref="A1:AD1"/>
   </mergeCells>
-  <dataValidations count="12">
+  <dataValidations count="11">
     <dataValidation sqref="H5:H57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"신규,추가,수정,개조,기타"</formula1>
     </dataValidation>
@@ -6657,9 +6665,6 @@
       <formula1>"제외"</formula1>
     </dataValidation>
     <dataValidation sqref="AB5:AB57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
-      <formula1>"제외"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AC5:AC57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"제외"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6709,18 +6714,18 @@
     <col width="12" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="30"/>
     <col width="8" customWidth="1" min="30" max="30"/>
-    <col width="10" customWidth="1" min="31" max="31"/>
-    <col width="8" customWidth="1" min="32" max="34"/>
-    <col width="8" customWidth="1" min="33" max="33"/>
-    <col width="8" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="34"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="39"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
-    <col width="13" customWidth="1" min="37" max="37"/>
-    <col width="13" customWidth="1" min="38" max="38"/>
-    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="8" customWidth="1" min="36" max="36"/>
+    <col width="8" customWidth="1" min="37" max="37"/>
+    <col width="8" customWidth="1" min="38" max="38"/>
+    <col width="8" customWidth="1" min="39" max="39"/>
     <col width="8" customWidth="1" min="40" max="45"/>
     <col width="8" customWidth="1" min="41" max="41"/>
-    <col width="8" customWidth="1" min="42" max="42"/>
+    <col width="9" customWidth="1" min="42" max="42"/>
     <col width="8" customWidth="1" min="43" max="43"/>
     <col width="8" customWidth="1" min="44" max="44"/>
     <col width="8" customWidth="1" min="45" max="45"/>
@@ -6729,7 +6734,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="104" t="inlineStr">
+      <c r="A1" s="116" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -6775,14 +6780,10 @@
       <c r="AN1" s="74" t="n"/>
       <c r="AO1" s="74" t="n"/>
       <c r="AP1" s="74" t="n"/>
-      <c r="AQ1" s="74" t="n"/>
-      <c r="AR1" s="74" t="n"/>
-      <c r="AS1" s="74" t="n"/>
-      <c r="AT1" s="74" t="n"/>
-      <c r="AU1" s="75" t="n"/>
+      <c r="AQ1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="105" t="inlineStr">
+      <c r="A2" s="117" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 진행현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -6827,11 +6828,12 @@
       <c r="AM2" s="74" t="n"/>
       <c r="AN2" s="74" t="n"/>
       <c r="AO2" s="74" t="n"/>
-      <c r="AP2" s="74" t="n"/>
-      <c r="AQ2" s="74" t="n"/>
-      <c r="AR2" s="74" t="n"/>
-      <c r="AS2" s="74" t="n"/>
-      <c r="AT2" s="75" t="n"/>
+      <c r="AP2" s="75" t="n"/>
+      <c r="AQ2" s="118" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:44</t>
+        </is>
+      </c>
       <c r="AU2" s="106" t="inlineStr">
         <is>
           <t>업데이트: 2026-05-02 01:42</t>
@@ -7251,80 +7253,80 @@
       </c>
       <c r="AE4" s="49" t="inlineStr">
         <is>
-          <t>가공팀
-프로그램</t>
-        </is>
-      </c>
-      <c r="AF4" s="49" t="inlineStr">
-        <is>
-          <t>가공팀
-가공</t>
-        </is>
-      </c>
-      <c r="AG4" s="49" t="inlineStr">
-        <is>
-          <t>가공팀
-후처리</t>
-        </is>
-      </c>
-      <c r="AH4" s="49" t="inlineStr">
-        <is>
-          <t>가공팀
-소계</t>
-        </is>
-      </c>
-      <c r="AI4" s="49" t="inlineStr">
-        <is>
           <t>제조기술2팀
 조립</t>
         </is>
       </c>
-      <c r="AJ4" s="49" t="inlineStr">
+      <c r="AF4" s="49" t="inlineStr">
         <is>
           <t>제조기술2팀
 전장</t>
         </is>
       </c>
-      <c r="AK4" s="49" t="inlineStr">
+      <c r="AG4" s="49" t="inlineStr">
         <is>
           <t>제조기술2팀
 TURN-ON</t>
         </is>
       </c>
-      <c r="AL4" s="49" t="inlineStr">
+      <c r="AH4" s="49" t="inlineStr">
         <is>
           <t>제조기술2팀
 IO체크</t>
         </is>
       </c>
-      <c r="AM4" s="49" t="inlineStr">
+      <c r="AI4" s="49" t="inlineStr">
         <is>
           <t>제조기술2팀
 소계</t>
         </is>
       </c>
-      <c r="AN4" s="49" t="inlineStr">
+      <c r="AJ4" s="49" t="inlineStr">
         <is>
           <t>베트남
 설계</t>
         </is>
       </c>
-      <c r="AO4" s="49" t="inlineStr">
+      <c r="AK4" s="49" t="inlineStr">
         <is>
           <t>베트남
 SW</t>
         </is>
       </c>
-      <c r="AP4" s="49" t="inlineStr">
+      <c r="AL4" s="49" t="inlineStr">
         <is>
           <t>베트남
 전장</t>
         </is>
       </c>
-      <c r="AQ4" s="49" t="inlineStr">
+      <c r="AM4" s="49" t="inlineStr">
         <is>
           <t>베트남
 가공</t>
+        </is>
+      </c>
+      <c r="AN4" s="49" t="inlineStr">
+        <is>
+          <t>베트남
+조립</t>
+        </is>
+      </c>
+      <c r="AO4" s="49" t="inlineStr">
+        <is>
+          <t>베트남
+DRYRUN</t>
+        </is>
+      </c>
+      <c r="AP4" s="49" t="inlineStr">
+        <is>
+          <t>베트남
+AUTORUN</t>
+        </is>
+      </c>
+      <c r="AQ4" s="49" t="inlineStr">
+        <is>
+          <t>베트남
+소계</t>
         </is>
       </c>
       <c r="AR4" s="49" t="inlineStr">
@@ -10586,8 +10588,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:AT2"/>
-    <mergeCell ref="A1:AU1"/>
+    <mergeCell ref="A1:AQ1"/>
+    <mergeCell ref="A2:AP2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -10630,7 +10632,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="104" t="inlineStr">
+      <c r="A1" s="116" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -10659,7 +10661,7 @@
       <c r="W1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="105" t="inlineStr">
+      <c r="A2" s="117" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -10685,9 +10687,9 @@
       <c r="T2" s="74" t="n"/>
       <c r="U2" s="74" t="n"/>
       <c r="V2" s="75" t="n"/>
-      <c r="W2" s="106" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:42</t>
+      <c r="W2" s="118" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:44</t>
         </is>
       </c>
     </row>
@@ -11698,7 +11700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE41"/>
+  <dimension ref="A1:AD41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11727,15 +11729,15 @@
     <col width="12" customWidth="1" style="97" min="24" max="24"/>
     <col width="14" customWidth="1" style="97" min="25" max="25"/>
     <col width="8" customWidth="1" style="97" min="26" max="27"/>
-    <col width="8" customWidth="1" style="97" min="27" max="27"/>
-    <col width="13" customWidth="1" style="97" min="28" max="28"/>
-    <col width="8" customWidth="1" style="97" min="29" max="29"/>
+    <col width="13" customWidth="1" style="97" min="27" max="27"/>
+    <col width="8" customWidth="1" style="97" min="28" max="28"/>
+    <col width="12" customWidth="1" style="97" min="29" max="29"/>
     <col width="12" customWidth="1" style="97" min="30" max="30"/>
     <col width="12" customWidth="1" style="97" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="104" t="inlineStr">
+      <c r="A1" s="116" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -11768,11 +11770,10 @@
       <c r="AA1" s="74" t="n"/>
       <c r="AB1" s="74" t="n"/>
       <c r="AC1" s="74" t="n"/>
-      <c r="AD1" s="74" t="n"/>
-      <c r="AE1" s="75" t="n"/>
+      <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="105" t="inlineStr">
+      <c r="A2" s="117" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -11804,8 +11805,12 @@
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="74" t="n"/>
       <c r="AB2" s="74" t="n"/>
-      <c r="AC2" s="74" t="n"/>
-      <c r="AD2" s="75" t="n"/>
+      <c r="AC2" s="75" t="n"/>
+      <c r="AD2" s="118" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:44</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">
@@ -13703,10 +13708,10 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:AE1"/>
-    <mergeCell ref="A2:AD2"/>
+    <mergeCell ref="A2:AC2"/>
+    <mergeCell ref="A1:AD1"/>
   </mergeCells>
-  <dataValidations count="12">
+  <dataValidations count="11">
     <dataValidation sqref="H5:H41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"신규,추가,수정,개조,기타"</formula1>
     </dataValidation>
@@ -13740,9 +13745,6 @@
     <dataValidation sqref="AB5:AB41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"제외"</formula1>
     </dataValidation>
-    <dataValidation sqref="AC5:AC41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
-      <formula1>"제외"</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -13770,7 +13772,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="104" t="inlineStr">
+      <c r="A1" s="116" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -13784,7 +13786,7 @@
       <c r="H1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="105" t="inlineStr">
+      <c r="A2" s="117" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -13795,9 +13797,9 @@
       <c r="E2" s="74" t="n"/>
       <c r="F2" s="74" t="n"/>
       <c r="G2" s="75" t="n"/>
-      <c r="H2" s="106" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:42</t>
+      <c r="H2" s="118" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:44</t>
         </is>
       </c>
     </row>
@@ -15403,7 +15405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -15416,7 +15418,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="104" t="inlineStr">
+      <c r="A1" s="116" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -15429,7 +15431,7 @@
       <c r="G1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="105" t="inlineStr">
+      <c r="A2" s="117" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -15439,9 +15441,9 @@
       <c r="D2" s="74" t="n"/>
       <c r="E2" s="74" t="n"/>
       <c r="F2" s="75" t="n"/>
-      <c r="G2" s="106" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:42</t>
+      <c r="G2" s="118" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:44</t>
         </is>
       </c>
     </row>
@@ -16593,69 +16595,6 @@
       <c r="E57" s="68" t="n"/>
       <c r="F57" s="50" t="n"/>
       <c r="G57" s="50" t="n"/>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="59" t="n"/>
-      <c r="B58" s="59" t="n"/>
-      <c r="C58" s="59" t="n"/>
-      <c r="D58" s="59" t="n"/>
-      <c r="E58" s="69" t="n"/>
-      <c r="F58" s="59" t="n"/>
-      <c r="G58" s="59" t="n"/>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="50" t="n"/>
-      <c r="B59" s="50" t="n"/>
-      <c r="C59" s="50" t="n"/>
-      <c r="D59" s="50" t="n"/>
-      <c r="E59" s="68" t="n"/>
-      <c r="F59" s="50" t="n"/>
-      <c r="G59" s="50" t="n"/>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="59" t="n"/>
-      <c r="B60" s="59" t="n"/>
-      <c r="C60" s="59" t="n"/>
-      <c r="D60" s="59" t="n"/>
-      <c r="E60" s="69" t="n"/>
-      <c r="F60" s="59" t="n"/>
-      <c r="G60" s="59" t="n"/>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="50" t="n"/>
-      <c r="B61" s="50" t="n"/>
-      <c r="C61" s="50" t="n"/>
-      <c r="D61" s="50" t="n"/>
-      <c r="E61" s="68" t="n"/>
-      <c r="F61" s="50" t="n"/>
-      <c r="G61" s="50" t="n"/>
-    </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="59" t="n"/>
-      <c r="B62" s="59" t="n"/>
-      <c r="C62" s="59" t="n"/>
-      <c r="D62" s="59" t="n"/>
-      <c r="E62" s="69" t="n"/>
-      <c r="F62" s="59" t="n"/>
-      <c r="G62" s="59" t="n"/>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="50" t="n"/>
-      <c r="B63" s="50" t="n"/>
-      <c r="C63" s="50" t="n"/>
-      <c r="D63" s="50" t="n"/>
-      <c r="E63" s="68" t="n"/>
-      <c r="F63" s="50" t="n"/>
-      <c r="G63" s="50" t="n"/>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="59" t="n"/>
-      <c r="B64" s="59" t="n"/>
-      <c r="C64" s="59" t="n"/>
-      <c r="D64" s="59" t="n"/>
-      <c r="E64" s="69" t="n"/>
-      <c r="F64" s="59" t="n"/>
-      <c r="G64" s="59" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
@@ -16675,7 +16614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -16687,7 +16626,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="104" t="inlineStr">
+      <c r="A1" s="116" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -16699,7 +16638,7 @@
       <c r="F1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="105" t="inlineStr">
+      <c r="A2" s="117" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -16708,9 +16647,9 @@
       <c r="C2" s="74" t="n"/>
       <c r="D2" s="74" t="n"/>
       <c r="E2" s="75" t="n"/>
-      <c r="F2" s="106" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:42</t>
+      <c r="F2" s="118" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:45</t>
         </is>
       </c>
     </row>
@@ -17707,62 +17646,6 @@
       <c r="D57" s="50" t="n"/>
       <c r="E57" s="68" t="n"/>
       <c r="F57" s="50" t="n"/>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="59" t="n"/>
-      <c r="B58" s="59" t="n"/>
-      <c r="C58" s="59" t="n"/>
-      <c r="D58" s="59" t="n"/>
-      <c r="E58" s="69" t="n"/>
-      <c r="F58" s="59" t="n"/>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="50" t="n"/>
-      <c r="B59" s="50" t="n"/>
-      <c r="C59" s="50" t="n"/>
-      <c r="D59" s="50" t="n"/>
-      <c r="E59" s="68" t="n"/>
-      <c r="F59" s="50" t="n"/>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="59" t="n"/>
-      <c r="B60" s="59" t="n"/>
-      <c r="C60" s="59" t="n"/>
-      <c r="D60" s="59" t="n"/>
-      <c r="E60" s="69" t="n"/>
-      <c r="F60" s="59" t="n"/>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="50" t="n"/>
-      <c r="B61" s="50" t="n"/>
-      <c r="C61" s="50" t="n"/>
-      <c r="D61" s="50" t="n"/>
-      <c r="E61" s="68" t="n"/>
-      <c r="F61" s="50" t="n"/>
-    </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="59" t="n"/>
-      <c r="B62" s="59" t="n"/>
-      <c r="C62" s="59" t="n"/>
-      <c r="D62" s="59" t="n"/>
-      <c r="E62" s="69" t="n"/>
-      <c r="F62" s="59" t="n"/>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="50" t="n"/>
-      <c r="B63" s="50" t="n"/>
-      <c r="C63" s="50" t="n"/>
-      <c r="D63" s="50" t="n"/>
-      <c r="E63" s="68" t="n"/>
-      <c r="F63" s="50" t="n"/>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="59" t="n"/>
-      <c r="B64" s="59" t="n"/>
-      <c r="C64" s="59" t="n"/>
-      <c r="D64" s="59" t="n"/>
-      <c r="E64" s="69" t="n"/>
-      <c r="F64" s="59" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
@@ -17781,7 +17664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE34"/>
+  <dimension ref="A1:AD34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -17810,15 +17693,15 @@
     <col width="12" customWidth="1" style="97" min="24" max="24"/>
     <col width="14" customWidth="1" style="97" min="25" max="25"/>
     <col width="8" customWidth="1" style="97" min="26" max="26"/>
-    <col width="8" customWidth="1" style="97" min="27" max="27"/>
-    <col width="13" customWidth="1" style="97" min="28" max="28"/>
-    <col width="8" customWidth="1" style="97" min="29" max="29"/>
+    <col width="13" customWidth="1" style="97" min="27" max="27"/>
+    <col width="8" customWidth="1" style="97" min="28" max="28"/>
+    <col width="12" customWidth="1" style="97" min="29" max="29"/>
     <col width="12" customWidth="1" style="97" min="30" max="30"/>
     <col width="12" customWidth="1" style="97" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="104" t="inlineStr">
+      <c r="A1" s="116" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -17851,11 +17734,10 @@
       <c r="AA1" s="74" t="n"/>
       <c r="AB1" s="74" t="n"/>
       <c r="AC1" s="74" t="n"/>
-      <c r="AD1" s="74" t="n"/>
-      <c r="AE1" s="75" t="n"/>
+      <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="105" t="inlineStr">
+      <c r="A2" s="117" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -17887,8 +17769,12 @@
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="74" t="n"/>
       <c r="AB2" s="74" t="n"/>
-      <c r="AC2" s="74" t="n"/>
-      <c r="AD2" s="75" t="n"/>
+      <c r="AC2" s="75" t="n"/>
+      <c r="AD2" s="118" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:45</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">
@@ -19160,10 +19046,10 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DEDA"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:AE1"/>
-    <mergeCell ref="A2:AD2"/>
+    <mergeCell ref="A2:AC2"/>
+    <mergeCell ref="A1:AD1"/>
   </mergeCells>
-  <dataValidations count="12">
+  <dataValidations count="11">
     <dataValidation sqref="H5:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"신규,추가,수정,개조,기타"</formula1>
     </dataValidation>
@@ -19197,9 +19083,6 @@
     <dataValidation sqref="AB5:AB34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
       <formula1>"제외"</formula1>
     </dataValidation>
-    <dataValidation sqref="AC5:AC34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
-      <formula1>"제외"</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
@@ -438,7 +438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
@@ -800,6 +800,24 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="29" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1180,14 +1198,24 @@
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
         <t>▣ 계산서
-발행일
-(직접 입력)</t>
+발행일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입금일
-(직접 입력)</t>
+        <t>▣ 입금일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="F22" authorId="0" shapeId="0">
@@ -1770,15 +1798,25 @@
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하구분
-(직접 입력)</t>
+        <t>▣ 출하구분 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
         <t>▣ INV번호
-(출하코드)
-(직접 입력)</t>
+(출하코드) (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
@@ -1828,26 +1866,46 @@
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 차수/경로
-(직접 입력)</t>
+        <t>▣ 차수/경로 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 거래유형
-(직접 입력)</t>
+        <t>▣ 거래유형 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통관분류
-(직접 입력)</t>
+        <t>▣ 통관분류 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하일
-(직접 입력)</t>
+        <t>▣ 출하일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
@@ -1862,8 +1920,13 @@
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 환율
-(직접 입력)</t>
+        <t>▣ 환율 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
@@ -1876,8 +1939,13 @@
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ BOX수
-(직접 입력)</t>
+        <t>▣ BOX수 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
@@ -1891,20 +1959,35 @@
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 인보이스(USD)
-(직접 입력)</t>
+        <t>▣ 인보이스(USD) (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통관상태
-(직접 입력)</t>
+        <t>▣ 부서 작업 상태
+• 드롭다운 선택:
+  미착수 — 작업 시작 안 함
+  진행중 — 작업 진행 중
+  완료   — 부서 작업 완료
+  N/A    — 해당 부서 무관 프로젝트
+• 부서장이 매주 상태 갱신 권장</t>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ VN입고일
-(직접 입력)</t>
+        <t>▣ VN입고일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
@@ -1919,22 +2002,37 @@
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
         <t>▣ 입고
-완료
-(직접 입력)</t>
+완료 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
         <t>▣ 출하
-완료
-(직접 입력)</t>
+완료 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
         <t>▣ 조달
-진행률
-(직접 입력)</t>
+진행률 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
   </commentList>
@@ -2235,14 +2333,24 @@
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
         <t>▣ 계산서
-발행일
-(직접 입력)</t>
+발행일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입금일
-(직접 입력)</t>
+        <t>▣ 입금일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
   </commentList>
@@ -2401,14 +2509,24 @@
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 발행일
-(직접 입력)</t>
+        <t>▣ 발행일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 발행사유
-(직접 입력)</t>
+        <t>▣ 발행사유 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
   </commentList>
@@ -2476,8 +2594,13 @@
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 생성일
-(직접 입력)</t>
+        <t>▣ 생성일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
   </commentList>
@@ -2778,14 +2901,24 @@
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
         <t>▣ 계산서
-발행일
-(직접 입력)</t>
+발행일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입금일
-(직접 입력)</t>
+        <t>▣ 입금일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
   </commentList>
@@ -3119,7 +3252,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="116" t="inlineStr">
+      <c r="A1" s="122" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -3155,7 +3288,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="117" t="inlineStr">
+      <c r="A2" s="123" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -3188,9 +3321,9 @@
       <c r="AA2" s="74" t="n"/>
       <c r="AB2" s="74" t="n"/>
       <c r="AC2" s="75" t="n"/>
-      <c r="AD2" s="118" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:44</t>
+      <c r="AD2" s="124" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:07</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6867,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="116" t="inlineStr">
+      <c r="A1" s="122" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -6783,7 +6916,7 @@
       <c r="AQ1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="117" t="inlineStr">
+      <c r="A2" s="123" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 진행현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -6829,12 +6962,12 @@
       <c r="AN2" s="74" t="n"/>
       <c r="AO2" s="74" t="n"/>
       <c r="AP2" s="75" t="n"/>
-      <c r="AQ2" s="118" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:44</t>
-        </is>
-      </c>
-      <c r="AU2" s="106" t="inlineStr">
+      <c r="AQ2" s="124" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:07</t>
+        </is>
+      </c>
+      <c r="AU2" s="121" t="inlineStr">
         <is>
           <t>업데이트: 2026-05-02 01:42</t>
         </is>
@@ -10632,7 +10765,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="116" t="inlineStr">
+      <c r="A1" s="122" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -10661,7 +10794,7 @@
       <c r="W1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="117" t="inlineStr">
+      <c r="A2" s="123" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -10687,9 +10820,9 @@
       <c r="T2" s="74" t="n"/>
       <c r="U2" s="74" t="n"/>
       <c r="V2" s="75" t="n"/>
-      <c r="W2" s="118" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:44</t>
+      <c r="W2" s="124" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:07</t>
         </is>
       </c>
     </row>
@@ -11737,7 +11870,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="116" t="inlineStr">
+      <c r="A1" s="122" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -11773,7 +11906,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="117" t="inlineStr">
+      <c r="A2" s="123" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -11806,9 +11939,9 @@
       <c r="AA2" s="74" t="n"/>
       <c r="AB2" s="74" t="n"/>
       <c r="AC2" s="75" t="n"/>
-      <c r="AD2" s="118" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:44</t>
+      <c r="AD2" s="124" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:07</t>
         </is>
       </c>
     </row>
@@ -13772,7 +13905,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="116" t="inlineStr">
+      <c r="A1" s="122" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -13786,7 +13919,7 @@
       <c r="H1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="117" t="inlineStr">
+      <c r="A2" s="123" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -13797,9 +13930,9 @@
       <c r="E2" s="74" t="n"/>
       <c r="F2" s="74" t="n"/>
       <c r="G2" s="75" t="n"/>
-      <c r="H2" s="118" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:44</t>
+      <c r="H2" s="124" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:07</t>
         </is>
       </c>
     </row>
@@ -15418,7 +15551,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="116" t="inlineStr">
+      <c r="A1" s="122" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -15431,7 +15564,7 @@
       <c r="G1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="117" t="inlineStr">
+      <c r="A2" s="123" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -15441,9 +15574,9 @@
       <c r="D2" s="74" t="n"/>
       <c r="E2" s="74" t="n"/>
       <c r="F2" s="75" t="n"/>
-      <c r="G2" s="118" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:44</t>
+      <c r="G2" s="124" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:07</t>
         </is>
       </c>
     </row>
@@ -16626,7 +16759,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="116" t="inlineStr">
+      <c r="A1" s="122" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -16638,7 +16771,7 @@
       <c r="F1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="117" t="inlineStr">
+      <c r="A2" s="123" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -16647,9 +16780,9 @@
       <c r="C2" s="74" t="n"/>
       <c r="D2" s="74" t="n"/>
       <c r="E2" s="75" t="n"/>
-      <c r="F2" s="118" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:45</t>
+      <c r="F2" s="124" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:07</t>
         </is>
       </c>
     </row>
@@ -17701,7 +17834,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="116" t="inlineStr">
+      <c r="A1" s="122" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -17737,7 +17870,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="117" t="inlineStr">
+      <c r="A2" s="123" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -17770,9 +17903,9 @@
       <c r="AA2" s="74" t="n"/>
       <c r="AB2" s="74" t="n"/>
       <c r="AC2" s="75" t="n"/>
-      <c r="AD2" s="118" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:45</t>
+      <c r="AD2" s="124" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:07</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
@@ -438,7 +438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
@@ -800,6 +800,15 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="29" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3252,7 +3261,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="122" t="inlineStr">
+      <c r="A1" s="125" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -3288,7 +3297,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="123" t="inlineStr">
+      <c r="A2" s="126" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -3321,9 +3330,9 @@
       <c r="AA2" s="74" t="n"/>
       <c r="AB2" s="74" t="n"/>
       <c r="AC2" s="75" t="n"/>
-      <c r="AD2" s="124" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:07</t>
+      <c r="AD2" s="127" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:00</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6876,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="122" t="inlineStr">
+      <c r="A1" s="125" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -6916,7 +6925,7 @@
       <c r="AQ1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="123" t="inlineStr">
+      <c r="A2" s="126" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 진행현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -6962,12 +6971,12 @@
       <c r="AN2" s="74" t="n"/>
       <c r="AO2" s="74" t="n"/>
       <c r="AP2" s="75" t="n"/>
-      <c r="AQ2" s="124" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:07</t>
-        </is>
-      </c>
-      <c r="AU2" s="121" t="inlineStr">
+      <c r="AQ2" s="127" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:00</t>
+        </is>
+      </c>
+      <c r="AU2" s="124" t="inlineStr">
         <is>
           <t>업데이트: 2026-05-02 01:42</t>
         </is>
@@ -10765,7 +10774,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="122" t="inlineStr">
+      <c r="A1" s="125" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -10794,7 +10803,7 @@
       <c r="W1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="123" t="inlineStr">
+      <c r="A2" s="126" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -10820,9 +10829,9 @@
       <c r="T2" s="74" t="n"/>
       <c r="U2" s="74" t="n"/>
       <c r="V2" s="75" t="n"/>
-      <c r="W2" s="124" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:07</t>
+      <c r="W2" s="127" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:01</t>
         </is>
       </c>
     </row>
@@ -11870,7 +11879,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="122" t="inlineStr">
+      <c r="A1" s="125" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -11906,7 +11915,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="123" t="inlineStr">
+      <c r="A2" s="126" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -11939,9 +11948,9 @@
       <c r="AA2" s="74" t="n"/>
       <c r="AB2" s="74" t="n"/>
       <c r="AC2" s="75" t="n"/>
-      <c r="AD2" s="124" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:07</t>
+      <c r="AD2" s="127" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:01</t>
         </is>
       </c>
     </row>
@@ -13905,7 +13914,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="122" t="inlineStr">
+      <c r="A1" s="125" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -13919,7 +13928,7 @@
       <c r="H1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="123" t="inlineStr">
+      <c r="A2" s="126" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -13930,9 +13939,9 @@
       <c r="E2" s="74" t="n"/>
       <c r="F2" s="74" t="n"/>
       <c r="G2" s="75" t="n"/>
-      <c r="H2" s="124" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:07</t>
+      <c r="H2" s="127" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:01</t>
         </is>
       </c>
     </row>
@@ -15551,7 +15560,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="122" t="inlineStr">
+      <c r="A1" s="125" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -15564,7 +15573,7 @@
       <c r="G1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="123" t="inlineStr">
+      <c r="A2" s="126" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -15574,9 +15583,9 @@
       <c r="D2" s="74" t="n"/>
       <c r="E2" s="74" t="n"/>
       <c r="F2" s="75" t="n"/>
-      <c r="G2" s="124" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:07</t>
+      <c r="G2" s="127" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:01</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16768,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="122" t="inlineStr">
+      <c r="A1" s="125" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -16771,7 +16780,7 @@
       <c r="F1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="123" t="inlineStr">
+      <c r="A2" s="126" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -16780,9 +16789,9 @@
       <c r="C2" s="74" t="n"/>
       <c r="D2" s="74" t="n"/>
       <c r="E2" s="75" t="n"/>
-      <c r="F2" s="124" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:07</t>
+      <c r="F2" s="127" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:01</t>
         </is>
       </c>
     </row>
@@ -17834,7 +17843,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="122" t="inlineStr">
+      <c r="A1" s="125" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -17870,7 +17879,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="123" t="inlineStr">
+      <c r="A2" s="126" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -17903,9 +17912,9 @@
       <c r="AA2" s="74" t="n"/>
       <c r="AB2" s="74" t="n"/>
       <c r="AC2" s="75" t="n"/>
-      <c r="AD2" s="124" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:07</t>
+      <c r="AD2" s="127" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:01</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
@@ -438,7 +438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
@@ -837,6 +837,15 @@
     <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1103,11 +1112,16 @@
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률(%)
-• 자동 계산 — 참여 부서 소계의 평균
-  예: 3개 부서 진척률 80/50/30 → 53%
-• sync 시 갱신, 수동 수정 불가
-• 100% = 전 부서 완료 상태</t>
+        <t>▣ 전체 진척률 (%)
+• 자동 계산 (수정 불가, sync 시 갱신)
+📌 사업부별 계산식:
+  ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
+    예: 7개 부서 중 '제외' 1, 완료 3 → 3/6 = 50%
+  ▸ 02 자동화  = 참여 부서 % 진척률 평균
+    예: 3개 부서 80/50/30% → 53%
+• '제외' 부서는 분모에서 빠짐
+• 100% = 전 참여 부서 완료
+• 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
@@ -1363,11 +1377,16 @@
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률(%)
-• 자동 계산 — 참여 부서 소계의 평균
-  예: 3개 부서 진척률 80/50/30 → 53%
-• sync 시 갱신, 수동 수정 불가
-• 100% = 전 부서 완료 상태</t>
+        <t>▣ 전체 진척률 (%)
+• 자동 계산 (수정 불가, sync 시 갱신)
+📌 사업부별 계산식:
+  ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
+    예: 7개 부서 중 '제외' 1, 완료 3 → 3/6 = 50%
+  ▸ 02 자동화  = 참여 부서 % 진척률 평균
+    예: 3개 부서 80/50/30% → 53%
+• '제외' 부서는 분모에서 빠짐
+• 100% = 전 참여 부서 완료
+• 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
@@ -2001,11 +2020,16 @@
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률(%)
-• 자동 계산 — 참여 부서 소계의 평균
-  예: 3개 부서 진척률 80/50/30 → 53%
-• sync 시 갱신, 수동 수정 불가
-• 100% = 전 부서 완료 상태</t>
+        <t>▣ 전체 진척률 (%)
+• 자동 계산 (수정 불가, sync 시 갱신)
+📌 사업부별 계산식:
+  ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
+    예: 7개 부서 중 '제외' 1, 완료 3 → 3/6 = 50%
+  ▸ 02 자동화  = 참여 부서 % 진척률 평균
+    예: 3개 부서 80/50/30% → 53%
+• '제외' 부서는 분모에서 빠짐
+• 100% = 전 참여 부서 완료
+• 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
@@ -2238,11 +2262,16 @@
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률(%)
-• 자동 계산 — 참여 부서 소계의 평균
-  예: 3개 부서 진척률 80/50/30 → 53%
-• sync 시 갱신, 수동 수정 불가
-• 100% = 전 부서 완료 상태</t>
+        <t>▣ 전체 진척률 (%)
+• 자동 계산 (수정 불가, sync 시 갱신)
+📌 사업부별 계산식:
+  ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
+    예: 7개 부서 중 '제외' 1, 완료 3 → 3/6 = 50%
+  ▸ 02 자동화  = 참여 부서 % 진척률 평균
+    예: 3개 부서 80/50/30% → 53%
+• '제외' 부서는 분모에서 빠짐
+• 100% = 전 참여 부서 완료
+• 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
@@ -2806,11 +2835,16 @@
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률(%)
-• 자동 계산 — 참여 부서 소계의 평균
-  예: 3개 부서 진척률 80/50/30 → 53%
-• sync 시 갱신, 수동 수정 불가
-• 100% = 전 부서 완료 상태</t>
+        <t>▣ 전체 진척률 (%)
+• 자동 계산 (수정 불가, sync 시 갱신)
+📌 사업부별 계산식:
+  ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
+    예: 7개 부서 중 '제외' 1, 완료 3 → 3/6 = 50%
+  ▸ 02 자동화  = 참여 부서 % 진척률 평균
+    예: 3개 부서 80/50/30% → 53%
+• '제외' 부서는 분모에서 빠짐
+• 100% = 전 참여 부서 완료
+• 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
@@ -3261,7 +3295,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="125" t="inlineStr">
+      <c r="A1" s="128" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -3297,7 +3331,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="126" t="inlineStr">
+      <c r="A2" s="129" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -3330,9 +3364,9 @@
       <c r="AA2" s="74" t="n"/>
       <c r="AB2" s="74" t="n"/>
       <c r="AC2" s="75" t="n"/>
-      <c r="AD2" s="127" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:00</t>
+      <c r="AD2" s="130" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:53</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6910,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="125" t="inlineStr">
+      <c r="A1" s="128" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -6925,7 +6959,7 @@
       <c r="AQ1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="126" t="inlineStr">
+      <c r="A2" s="129" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 진행현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -6971,12 +7005,12 @@
       <c r="AN2" s="74" t="n"/>
       <c r="AO2" s="74" t="n"/>
       <c r="AP2" s="75" t="n"/>
-      <c r="AQ2" s="127" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:00</t>
-        </is>
-      </c>
-      <c r="AU2" s="124" t="inlineStr">
+      <c r="AQ2" s="130" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:53</t>
+        </is>
+      </c>
+      <c r="AU2" s="127" t="inlineStr">
         <is>
           <t>업데이트: 2026-05-02 01:42</t>
         </is>
@@ -10774,7 +10808,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="125" t="inlineStr">
+      <c r="A1" s="128" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -10803,7 +10837,7 @@
       <c r="W1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="126" t="inlineStr">
+      <c r="A2" s="129" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -10829,9 +10863,9 @@
       <c r="T2" s="74" t="n"/>
       <c r="U2" s="74" t="n"/>
       <c r="V2" s="75" t="n"/>
-      <c r="W2" s="127" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:01</t>
+      <c r="W2" s="130" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:53</t>
         </is>
       </c>
     </row>
@@ -11879,7 +11913,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="125" t="inlineStr">
+      <c r="A1" s="128" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -11915,7 +11949,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="126" t="inlineStr">
+      <c r="A2" s="129" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -11948,9 +11982,9 @@
       <c r="AA2" s="74" t="n"/>
       <c r="AB2" s="74" t="n"/>
       <c r="AC2" s="75" t="n"/>
-      <c r="AD2" s="127" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:01</t>
+      <c r="AD2" s="130" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:53</t>
         </is>
       </c>
     </row>
@@ -13914,7 +13948,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="125" t="inlineStr">
+      <c r="A1" s="128" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -13928,7 +13962,7 @@
       <c r="H1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="126" t="inlineStr">
+      <c r="A2" s="129" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -13939,9 +13973,9 @@
       <c r="E2" s="74" t="n"/>
       <c r="F2" s="74" t="n"/>
       <c r="G2" s="75" t="n"/>
-      <c r="H2" s="127" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:01</t>
+      <c r="H2" s="130" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:54</t>
         </is>
       </c>
     </row>
@@ -15560,7 +15594,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="125" t="inlineStr">
+      <c r="A1" s="128" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -15573,7 +15607,7 @@
       <c r="G1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="126" t="inlineStr">
+      <c r="A2" s="129" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -15583,9 +15617,9 @@
       <c r="D2" s="74" t="n"/>
       <c r="E2" s="74" t="n"/>
       <c r="F2" s="75" t="n"/>
-      <c r="G2" s="127" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:01</t>
+      <c r="G2" s="130" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:54</t>
         </is>
       </c>
     </row>
@@ -16768,7 +16802,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="125" t="inlineStr">
+      <c r="A1" s="128" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -16780,7 +16814,7 @@
       <c r="F1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="126" t="inlineStr">
+      <c r="A2" s="129" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -16789,9 +16823,9 @@
       <c r="C2" s="74" t="n"/>
       <c r="D2" s="74" t="n"/>
       <c r="E2" s="75" t="n"/>
-      <c r="F2" s="127" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:01</t>
+      <c r="F2" s="130" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:54</t>
         </is>
       </c>
     </row>
@@ -17843,7 +17877,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="125" t="inlineStr">
+      <c r="A1" s="128" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -17879,7 +17913,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="126" t="inlineStr">
+      <c r="A2" s="129" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -17912,9 +17946,9 @@
       <c r="AA2" s="74" t="n"/>
       <c r="AB2" s="74" t="n"/>
       <c r="AC2" s="75" t="n"/>
-      <c r="AD2" s="127" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:01</t>
+      <c r="AD2" s="130" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:54</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
@@ -3738,7 +3738,7 @@
       <c r="N5" s="54" t="n">
         <v>56900000</v>
       </c>
-      <c r="O5" s="55" t="n">
+      <c r="O5" s="78" t="n">
         <v>227600000</v>
       </c>
       <c r="P5" s="56" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="R5" s="51" t="n"/>
       <c r="S5" s="57" t="n">
-        <v>0.009166666666666667</v>
+        <v>0.15</v>
       </c>
       <c r="T5" s="58" t="n">
         <v>16</v>
@@ -3838,7 +3838,7 @@
       <c r="N6" s="63" t="n">
         <v>75840000</v>
       </c>
-      <c r="O6" s="64" t="n">
+      <c r="O6" s="79" t="n">
         <v>75840000</v>
       </c>
       <c r="P6" s="65" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="R6" s="60" t="n"/>
       <c r="S6" s="66" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="T6" s="67" t="n">
         <v>13</v>
@@ -3934,7 +3934,7 @@
       <c r="N7" s="54" t="n">
         <v>230700000</v>
       </c>
-      <c r="O7" s="55" t="n">
+      <c r="O7" s="78" t="n">
         <v>1614900000</v>
       </c>
       <c r="P7" s="56" t="inlineStr">
@@ -4032,7 +4032,7 @@
       <c r="N8" s="63" t="n">
         <v>230700000</v>
       </c>
-      <c r="O8" s="64" t="n">
+      <c r="O8" s="79" t="n">
         <v>1614900000</v>
       </c>
       <c r="P8" s="65" t="inlineStr">
@@ -4130,7 +4130,7 @@
       <c r="N9" s="54" t="n">
         <v>26000000</v>
       </c>
-      <c r="O9" s="55" t="n">
+      <c r="O9" s="78" t="n">
         <v>104000000</v>
       </c>
       <c r="P9" s="56" t="inlineStr">
@@ -4224,7 +4224,7 @@
       <c r="N10" s="63" t="n">
         <v>230700000</v>
       </c>
-      <c r="O10" s="64" t="n">
+      <c r="O10" s="79" t="n">
         <v>1845600000</v>
       </c>
       <c r="P10" s="65" t="inlineStr">
@@ -4318,7 +4318,7 @@
       <c r="N11" s="54" t="n">
         <v>254500000</v>
       </c>
-      <c r="O11" s="55" t="n">
+      <c r="O11" s="78" t="n">
         <v>254500000</v>
       </c>
       <c r="P11" s="56" t="inlineStr">
@@ -4412,7 +4412,7 @@
       <c r="N12" s="63" t="n">
         <v>227700000</v>
       </c>
-      <c r="O12" s="64" t="n">
+      <c r="O12" s="79" t="n">
         <v>1138500000</v>
       </c>
       <c r="P12" s="65" t="inlineStr">
@@ -4506,7 +4506,7 @@
       <c r="N13" s="54" t="n">
         <v>230700000</v>
       </c>
-      <c r="O13" s="55" t="n">
+      <c r="O13" s="78" t="n">
         <v>1384200000</v>
       </c>
       <c r="P13" s="56" t="inlineStr">
@@ -4600,7 +4600,7 @@
       <c r="N14" s="63" t="n">
         <v>248900000</v>
       </c>
-      <c r="O14" s="64" t="n">
+      <c r="O14" s="79" t="n">
         <v>995600000</v>
       </c>
       <c r="P14" s="65" t="inlineStr">
@@ -4694,7 +4694,7 @@
       <c r="N15" s="54" t="n">
         <v>248900000</v>
       </c>
-      <c r="O15" s="55" t="n">
+      <c r="O15" s="78" t="n">
         <v>746700000</v>
       </c>
       <c r="P15" s="56" t="inlineStr">
@@ -4788,7 +4788,7 @@
       <c r="N16" s="63" t="n">
         <v>65810000</v>
       </c>
-      <c r="O16" s="64" t="n">
+      <c r="O16" s="79" t="n">
         <v>131620000</v>
       </c>
       <c r="P16" s="65" t="inlineStr">
@@ -4802,9 +4802,7 @@
         </is>
       </c>
       <c r="R16" s="60" t="n"/>
-      <c r="S16" s="66" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="S16" s="66" t="n"/>
       <c r="T16" s="67" t="n"/>
       <c r="U16" s="59" t="inlineStr">
         <is>
@@ -4886,7 +4884,7 @@
       <c r="N17" s="54" t="n">
         <v>59750000</v>
       </c>
-      <c r="O17" s="55" t="n">
+      <c r="O17" s="78" t="n">
         <v>119500000</v>
       </c>
       <c r="P17" s="56" t="inlineStr">
@@ -4900,9 +4898,7 @@
         </is>
       </c>
       <c r="R17" s="51" t="n"/>
-      <c r="S17" s="57" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="S17" s="57" t="n"/>
       <c r="T17" s="58" t="n"/>
       <c r="U17" s="50" t="inlineStr">
         <is>
@@ -4984,7 +4980,7 @@
       <c r="N18" s="63" t="n">
         <v>59290000</v>
       </c>
-      <c r="O18" s="64" t="n">
+      <c r="O18" s="79" t="n">
         <v>59290000</v>
       </c>
       <c r="P18" s="65" t="inlineStr">
@@ -5076,7 +5072,7 @@
       <c r="N19" s="54" t="n">
         <v>26000000</v>
       </c>
-      <c r="O19" s="55" t="n">
+      <c r="O19" s="78" t="n">
         <v>26000000</v>
       </c>
       <c r="P19" s="56" t="inlineStr">
@@ -5168,7 +5164,7 @@
       <c r="N20" s="63" t="n">
         <v>28000000</v>
       </c>
-      <c r="O20" s="64" t="n">
+      <c r="O20" s="79" t="n">
         <v>28000000</v>
       </c>
       <c r="P20" s="65" t="inlineStr">
@@ -5260,7 +5256,7 @@
       <c r="N21" s="54" t="n">
         <v>36010000</v>
       </c>
-      <c r="O21" s="55" t="n">
+      <c r="O21" s="78" t="n">
         <v>36010000</v>
       </c>
       <c r="P21" s="56" t="inlineStr">
@@ -5311,12 +5307,12 @@
         </is>
       </c>
       <c r="E22" s="60" t="n"/>
-      <c r="F22" s="61" t="inlineStr">
+      <c r="F22" s="108" t="inlineStr">
         <is>
           <t>Display 압착 자동화설비</t>
         </is>
       </c>
-      <c r="G22" s="61" t="inlineStr">
+      <c r="G22" s="108" t="inlineStr">
         <is>
           <t>BATTPRESSAUTO-S-V2</t>
         </is>
@@ -5352,7 +5348,7 @@
       <c r="N22" s="63" t="n">
         <v>25779</v>
       </c>
-      <c r="O22" s="64" t="n">
+      <c r="O22" s="79" t="n">
         <v>232011</v>
       </c>
       <c r="P22" s="65" t="inlineStr">
@@ -5403,12 +5399,12 @@
         </is>
       </c>
       <c r="E23" s="51" t="n"/>
-      <c r="F23" s="52" t="inlineStr">
+      <c r="F23" s="107" t="inlineStr">
         <is>
           <t>지문센서조립 자동화 설비</t>
         </is>
       </c>
-      <c r="G23" s="52" t="inlineStr">
+      <c r="G23" s="107" t="inlineStr">
         <is>
           <t>FINGERASSY-S-V1</t>
         </is>
@@ -5444,7 +5440,7 @@
       <c r="N23" s="54" t="n">
         <v>49055</v>
       </c>
-      <c r="O23" s="55" t="n">
+      <c r="O23" s="78" t="n">
         <v>196220</v>
       </c>
       <c r="P23" s="56" t="inlineStr">
@@ -5495,12 +5491,12 @@
         </is>
       </c>
       <c r="E24" s="60" t="n"/>
-      <c r="F24" s="61" t="inlineStr">
+      <c r="F24" s="107" t="inlineStr">
         <is>
           <t>지문센서조립 자동화 설비</t>
         </is>
       </c>
-      <c r="G24" s="61" t="inlineStr">
+      <c r="G24" s="107" t="inlineStr">
         <is>
           <t>지문센서 조립기 변위 센서 IL-100, IL-1000, OP-87056, 개조품DL-RS1A, 가공품</t>
         </is>
@@ -5536,7 +5532,7 @@
       <c r="N24" s="63" t="n">
         <v>1480000</v>
       </c>
-      <c r="O24" s="64" t="n">
+      <c r="O24" s="79" t="n">
         <v>7400000</v>
       </c>
       <c r="P24" s="65" t="inlineStr">
@@ -5628,7 +5624,7 @@
       <c r="N25" s="54" t="n">
         <v>241900000</v>
       </c>
-      <c r="O25" s="55" t="n">
+      <c r="O25" s="78" t="n">
         <v>241900000</v>
       </c>
       <c r="P25" s="56" t="inlineStr">
@@ -5720,7 +5716,7 @@
       <c r="N26" s="63" t="n">
         <v>241900000</v>
       </c>
-      <c r="O26" s="64" t="n">
+      <c r="O26" s="79" t="n">
         <v>2902800000</v>
       </c>
       <c r="P26" s="65" t="inlineStr">
@@ -5812,7 +5808,7 @@
       <c r="N27" s="54" t="n">
         <v>98000000</v>
       </c>
-      <c r="O27" s="55" t="n">
+      <c r="O27" s="78" t="n">
         <v>98000000</v>
       </c>
       <c r="P27" s="56" t="inlineStr">
@@ -7010,7 +7006,7 @@
           <t>업데이트: 2026-05-03 11:53</t>
         </is>
       </c>
-      <c r="AU2" s="127" t="inlineStr">
+      <c r="AU2" s="130" t="inlineStr">
         <is>
           <t>업데이트: 2026-05-02 01:42</t>
         </is>
@@ -7565,25 +7561,25 @@
         </is>
       </c>
       <c r="H5" s="57" t="n">
-        <v>0.009166666666666667</v>
+        <v>0.15</v>
       </c>
       <c r="I5" s="57" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="J5" s="57" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="K5" s="57" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="L5" s="57" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="M5" s="57" t="n">
-        <v>0.005</v>
+        <v>0.5</v>
       </c>
       <c r="N5" s="57" t="n">
-        <v>0.009166666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="O5" s="57" t="n"/>
       <c r="P5" s="57" t="n"/>
@@ -7654,25 +7650,25 @@
         </is>
       </c>
       <c r="H6" s="66" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="I6" s="66" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="J6" s="66" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="K6" s="66" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="L6" s="66" t="n">
-        <v>0.008</v>
+        <v>0.8</v>
       </c>
       <c r="M6" s="66" t="n">
-        <v>0.001</v>
+        <v>0.1</v>
       </c>
       <c r="N6" s="66" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="O6" s="66" t="n"/>
       <c r="P6" s="66" t="n"/>
@@ -7777,7 +7773,11 @@
       <c r="AN7" s="57" t="n"/>
       <c r="AO7" s="57" t="n"/>
       <c r="AP7" s="57" t="n"/>
-      <c r="AQ7" s="57" t="n"/>
+      <c r="AQ7" s="57" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
       <c r="AR7" s="57" t="n"/>
       <c r="AS7" s="57" t="n"/>
       <c r="AT7" s="57" t="n"/>
@@ -7852,7 +7852,11 @@
       <c r="AN8" s="66" t="n"/>
       <c r="AO8" s="66" t="n"/>
       <c r="AP8" s="66" t="n"/>
-      <c r="AQ8" s="66" t="n"/>
+      <c r="AQ8" s="66" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
       <c r="AR8" s="66" t="n"/>
       <c r="AS8" s="66" t="n"/>
       <c r="AT8" s="66" t="n"/>
@@ -8002,7 +8006,11 @@
       <c r="AN10" s="66" t="n"/>
       <c r="AO10" s="66" t="n"/>
       <c r="AP10" s="66" t="n"/>
-      <c r="AQ10" s="66" t="n"/>
+      <c r="AQ10" s="66" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
       <c r="AR10" s="66" t="n"/>
       <c r="AS10" s="66" t="n"/>
       <c r="AT10" s="66" t="n"/>
@@ -8227,7 +8235,11 @@
       <c r="AN13" s="57" t="n"/>
       <c r="AO13" s="57" t="n"/>
       <c r="AP13" s="57" t="n"/>
-      <c r="AQ13" s="57" t="n"/>
+      <c r="AQ13" s="57" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
       <c r="AR13" s="57" t="n"/>
       <c r="AS13" s="57" t="n"/>
       <c r="AT13" s="57" t="n"/>
@@ -8417,17 +8429,13 @@
           <t>진행중</t>
         </is>
       </c>
-      <c r="H16" s="66" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="H16" s="66" t="n"/>
       <c r="I16" s="66" t="n"/>
       <c r="J16" s="66" t="n"/>
       <c r="K16" s="66" t="n"/>
       <c r="L16" s="66" t="n"/>
       <c r="M16" s="66" t="n"/>
-      <c r="N16" s="66" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="N16" s="66" t="n"/>
       <c r="O16" s="66" t="n"/>
       <c r="P16" s="66" t="n"/>
       <c r="Q16" s="66" t="n"/>
@@ -8496,17 +8504,13 @@
           <t>진행중</t>
         </is>
       </c>
-      <c r="H17" s="57" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="H17" s="57" t="n"/>
       <c r="I17" s="57" t="n"/>
       <c r="J17" s="57" t="n"/>
       <c r="K17" s="57" t="n"/>
       <c r="L17" s="57" t="n"/>
       <c r="M17" s="57" t="n"/>
-      <c r="N17" s="57" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="N17" s="57" t="n"/>
       <c r="O17" s="57" t="n"/>
       <c r="P17" s="57" t="n"/>
       <c r="Q17" s="57" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
@@ -438,7 +438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
@@ -846,6 +846,24 @@
     <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -930,15 +948,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -952,54 +985,102 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사담당자 (고객사 PIC)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -1010,11 +1091,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -1029,90 +1118,170 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당영업 (영업 담당자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PM (Project Manager)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수량
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통화 (KRW / USD)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 단가 (계약 단가)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 금액 (계약 총액)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주일 (공식 수주 일자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 납기일 (납품 약속일)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하경로 (물류 루트)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -1122,105 +1291,185 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ D-day (납기 카운터)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 비고 (자유 메모)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 계산서
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 계산서
 발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
@@ -1228,69 +1477,126 @@
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입금일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="F22" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R22)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R22)
 관리코드 003M2509의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="G22" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R22)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R22)
 관리코드 003M2509의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="F23" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 003M2509 모델 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 003M2509 모델 불일치
 권위(R22): Display 압착 자동화설비
 현재(R23): 지문센서조립 자동화 설비
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="G23" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 003M2509 품명 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 003M2509 품명 불일치
 권위(R22): BATTPRESSAUTO-S-V2
 현재(R23): FINGERASSY-S-V1
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="F24" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 003M2509 모델 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 003M2509 모델 불일치
 권위(R22): Display 압착 자동화설비
 현재(R24): 지문센서조립 자동화 설비
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="G24" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 003M2509 품명 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 003M2509 품명 불일치
 권위(R22): BATTPRESSAUTO-S-V2
 현재(R24): 지문센서 조립기 변위 센서 IL-100, IL-1000, OP-87056, 개조품DL-RS1A, 가공품
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1305,15 +1611,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -1327,57 +1648,105 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -1387,423 +1756,736 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AE4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AF4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AG4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AH4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AI4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AJ4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AK4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AL4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AM4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AN4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AO4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AP4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AQ4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AR4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AS4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AT4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AU4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1818,26 +2500,49 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하구분 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하구분 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ INV번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ INV번호
 (출하코드) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
@@ -1845,11 +2550,19 @@
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -1863,164 +2576,292 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 차수/경로 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 차수/경로 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 거래유형 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 거래유형 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통관분류 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통관분류 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통화 (KRW / USD)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 환율 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 환율 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수량
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ BOX수 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ BOX수 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 금액 (계약 총액)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 인보이스(USD) (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 인보이스(USD) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ VN입고일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ VN입고일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -2030,11 +2871,19 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입고
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입고
 완료 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
@@ -2042,11 +2891,19 @@
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하
 완료 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
@@ -2054,11 +2911,19 @@
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 조달
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 조달
 진행률 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
@@ -2066,6 +2931,7 @@
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2080,15 +2946,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2102,54 +2983,102 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사담당자 (고객사 PIC)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -2160,11 +3089,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -2179,90 +3116,170 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당영업 (영업 담당자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PM (Project Manager)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수량
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통화 (KRW / USD)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 단가 (계약 단가)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 금액 (계약 총액)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주일 (공식 수주 일자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 납기일 (납품 약속일)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하경로 (물류 루트)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -2272,105 +3289,185 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ D-day (납기 카운터)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 비고 (자유 메모)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 계산서
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 계산서
 발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
@@ -2378,17 +3475,26 @@
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입금일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2403,15 +3509,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2425,61 +3546,110 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주일 (공식 수주 일자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2494,15 +3664,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2516,55 +3701,96 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 발행일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 발행사유 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 발행사유 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2579,26 +3805,49 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2612,33 +3861,58 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 생성일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 생성일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2653,15 +3927,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2675,54 +3964,102 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사담당자 (고객사 PIC)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -2733,11 +4070,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -2752,90 +4097,170 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당영업 (영업 담당자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PM (Project Manager)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수량
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통화 (KRW / USD)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 단가 (계약 단가)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 금액 (계약 총액)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주일 (공식 수주 일자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 납기일 (납품 약속일)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하경로 (물류 루트)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -2845,105 +4270,185 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ D-day (납기 카운터)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 비고 (자유 메모)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 계산서
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 계산서
 발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
@@ -2951,17 +4456,26 @@
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입금일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -3295,7 +4809,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="128" t="inlineStr">
+      <c r="A1" s="134" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -3331,7 +4845,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="129" t="inlineStr">
+      <c r="A2" s="135" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -3364,9 +4878,9 @@
       <c r="AA2" s="74" t="n"/>
       <c r="AB2" s="74" t="n"/>
       <c r="AC2" s="75" t="n"/>
-      <c r="AD2" s="130" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:53</t>
+      <c r="AD2" s="136" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:33</t>
         </is>
       </c>
     </row>
@@ -3738,7 +5252,7 @@
       <c r="N5" s="54" t="n">
         <v>56900000</v>
       </c>
-      <c r="O5" s="78" t="n">
+      <c r="O5" s="55" t="n">
         <v>227600000</v>
       </c>
       <c r="P5" s="56" t="inlineStr">
@@ -3838,7 +5352,7 @@
       <c r="N6" s="63" t="n">
         <v>75840000</v>
       </c>
-      <c r="O6" s="79" t="n">
+      <c r="O6" s="64" t="n">
         <v>75840000</v>
       </c>
       <c r="P6" s="65" t="inlineStr">
@@ -3934,7 +5448,7 @@
       <c r="N7" s="54" t="n">
         <v>230700000</v>
       </c>
-      <c r="O7" s="78" t="n">
+      <c r="O7" s="55" t="n">
         <v>1614900000</v>
       </c>
       <c r="P7" s="56" t="inlineStr">
@@ -4032,7 +5546,7 @@
       <c r="N8" s="63" t="n">
         <v>230700000</v>
       </c>
-      <c r="O8" s="79" t="n">
+      <c r="O8" s="64" t="n">
         <v>1614900000</v>
       </c>
       <c r="P8" s="65" t="inlineStr">
@@ -4130,7 +5644,7 @@
       <c r="N9" s="54" t="n">
         <v>26000000</v>
       </c>
-      <c r="O9" s="78" t="n">
+      <c r="O9" s="55" t="n">
         <v>104000000</v>
       </c>
       <c r="P9" s="56" t="inlineStr">
@@ -4224,7 +5738,7 @@
       <c r="N10" s="63" t="n">
         <v>230700000</v>
       </c>
-      <c r="O10" s="79" t="n">
+      <c r="O10" s="64" t="n">
         <v>1845600000</v>
       </c>
       <c r="P10" s="65" t="inlineStr">
@@ -4318,7 +5832,7 @@
       <c r="N11" s="54" t="n">
         <v>254500000</v>
       </c>
-      <c r="O11" s="78" t="n">
+      <c r="O11" s="55" t="n">
         <v>254500000</v>
       </c>
       <c r="P11" s="56" t="inlineStr">
@@ -4412,7 +5926,7 @@
       <c r="N12" s="63" t="n">
         <v>227700000</v>
       </c>
-      <c r="O12" s="79" t="n">
+      <c r="O12" s="64" t="n">
         <v>1138500000</v>
       </c>
       <c r="P12" s="65" t="inlineStr">
@@ -4506,7 +6020,7 @@
       <c r="N13" s="54" t="n">
         <v>230700000</v>
       </c>
-      <c r="O13" s="78" t="n">
+      <c r="O13" s="55" t="n">
         <v>1384200000</v>
       </c>
       <c r="P13" s="56" t="inlineStr">
@@ -4600,7 +6114,7 @@
       <c r="N14" s="63" t="n">
         <v>248900000</v>
       </c>
-      <c r="O14" s="79" t="n">
+      <c r="O14" s="64" t="n">
         <v>995600000</v>
       </c>
       <c r="P14" s="65" t="inlineStr">
@@ -4694,7 +6208,7 @@
       <c r="N15" s="54" t="n">
         <v>248900000</v>
       </c>
-      <c r="O15" s="78" t="n">
+      <c r="O15" s="55" t="n">
         <v>746700000</v>
       </c>
       <c r="P15" s="56" t="inlineStr">
@@ -4788,7 +6302,7 @@
       <c r="N16" s="63" t="n">
         <v>65810000</v>
       </c>
-      <c r="O16" s="79" t="n">
+      <c r="O16" s="64" t="n">
         <v>131620000</v>
       </c>
       <c r="P16" s="65" t="inlineStr">
@@ -4884,7 +6398,7 @@
       <c r="N17" s="54" t="n">
         <v>59750000</v>
       </c>
-      <c r="O17" s="78" t="n">
+      <c r="O17" s="55" t="n">
         <v>119500000</v>
       </c>
       <c r="P17" s="56" t="inlineStr">
@@ -4980,7 +6494,7 @@
       <c r="N18" s="63" t="n">
         <v>59290000</v>
       </c>
-      <c r="O18" s="79" t="n">
+      <c r="O18" s="64" t="n">
         <v>59290000</v>
       </c>
       <c r="P18" s="65" t="inlineStr">
@@ -5072,7 +6586,7 @@
       <c r="N19" s="54" t="n">
         <v>26000000</v>
       </c>
-      <c r="O19" s="78" t="n">
+      <c r="O19" s="55" t="n">
         <v>26000000</v>
       </c>
       <c r="P19" s="56" t="inlineStr">
@@ -5164,7 +6678,7 @@
       <c r="N20" s="63" t="n">
         <v>28000000</v>
       </c>
-      <c r="O20" s="79" t="n">
+      <c r="O20" s="64" t="n">
         <v>28000000</v>
       </c>
       <c r="P20" s="65" t="inlineStr">
@@ -5256,7 +6770,7 @@
       <c r="N21" s="54" t="n">
         <v>36010000</v>
       </c>
-      <c r="O21" s="78" t="n">
+      <c r="O21" s="55" t="n">
         <v>36010000</v>
       </c>
       <c r="P21" s="56" t="inlineStr">
@@ -5307,12 +6821,12 @@
         </is>
       </c>
       <c r="E22" s="60" t="n"/>
-      <c r="F22" s="108" t="inlineStr">
+      <c r="F22" s="61" t="inlineStr">
         <is>
           <t>Display 압착 자동화설비</t>
         </is>
       </c>
-      <c r="G22" s="108" t="inlineStr">
+      <c r="G22" s="61" t="inlineStr">
         <is>
           <t>BATTPRESSAUTO-S-V2</t>
         </is>
@@ -5348,7 +6862,7 @@
       <c r="N22" s="63" t="n">
         <v>25779</v>
       </c>
-      <c r="O22" s="79" t="n">
+      <c r="O22" s="64" t="n">
         <v>232011</v>
       </c>
       <c r="P22" s="65" t="inlineStr">
@@ -5399,12 +6913,12 @@
         </is>
       </c>
       <c r="E23" s="51" t="n"/>
-      <c r="F23" s="107" t="inlineStr">
+      <c r="F23" s="52" t="inlineStr">
         <is>
           <t>지문센서조립 자동화 설비</t>
         </is>
       </c>
-      <c r="G23" s="107" t="inlineStr">
+      <c r="G23" s="52" t="inlineStr">
         <is>
           <t>FINGERASSY-S-V1</t>
         </is>
@@ -5440,7 +6954,7 @@
       <c r="N23" s="54" t="n">
         <v>49055</v>
       </c>
-      <c r="O23" s="78" t="n">
+      <c r="O23" s="55" t="n">
         <v>196220</v>
       </c>
       <c r="P23" s="56" t="inlineStr">
@@ -5491,12 +7005,12 @@
         </is>
       </c>
       <c r="E24" s="60" t="n"/>
-      <c r="F24" s="107" t="inlineStr">
+      <c r="F24" s="61" t="inlineStr">
         <is>
           <t>지문센서조립 자동화 설비</t>
         </is>
       </c>
-      <c r="G24" s="107" t="inlineStr">
+      <c r="G24" s="61" t="inlineStr">
         <is>
           <t>지문센서 조립기 변위 센서 IL-100, IL-1000, OP-87056, 개조품DL-RS1A, 가공품</t>
         </is>
@@ -5532,7 +7046,7 @@
       <c r="N24" s="63" t="n">
         <v>1480000</v>
       </c>
-      <c r="O24" s="79" t="n">
+      <c r="O24" s="64" t="n">
         <v>7400000</v>
       </c>
       <c r="P24" s="65" t="inlineStr">
@@ -5624,7 +7138,7 @@
       <c r="N25" s="54" t="n">
         <v>241900000</v>
       </c>
-      <c r="O25" s="78" t="n">
+      <c r="O25" s="55" t="n">
         <v>241900000</v>
       </c>
       <c r="P25" s="56" t="inlineStr">
@@ -5716,7 +7230,7 @@
       <c r="N26" s="63" t="n">
         <v>241900000</v>
       </c>
-      <c r="O26" s="79" t="n">
+      <c r="O26" s="64" t="n">
         <v>2902800000</v>
       </c>
       <c r="P26" s="65" t="inlineStr">
@@ -5808,7 +7322,7 @@
       <c r="N27" s="54" t="n">
         <v>98000000</v>
       </c>
-      <c r="O27" s="78" t="n">
+      <c r="O27" s="55" t="n">
         <v>98000000</v>
       </c>
       <c r="P27" s="56" t="inlineStr">
@@ -6906,7 +8420,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="128" t="inlineStr">
+      <c r="A1" s="134" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -6955,7 +8469,7 @@
       <c r="AQ1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="129" t="inlineStr">
+      <c r="A2" s="135" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 진행현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -7001,12 +8515,12 @@
       <c r="AN2" s="74" t="n"/>
       <c r="AO2" s="74" t="n"/>
       <c r="AP2" s="75" t="n"/>
-      <c r="AQ2" s="130" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:53</t>
-        </is>
-      </c>
-      <c r="AU2" s="130" t="inlineStr">
+      <c r="AQ2" s="136" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:33</t>
+        </is>
+      </c>
+      <c r="AU2" s="133" t="inlineStr">
         <is>
           <t>업데이트: 2026-05-02 01:42</t>
         </is>
@@ -10812,7 +12326,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="128" t="inlineStr">
+      <c r="A1" s="134" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -10841,7 +12355,7 @@
       <c r="W1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="129" t="inlineStr">
+      <c r="A2" s="135" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -10867,9 +12381,9 @@
       <c r="T2" s="74" t="n"/>
       <c r="U2" s="74" t="n"/>
       <c r="V2" s="75" t="n"/>
-      <c r="W2" s="130" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:53</t>
+      <c r="W2" s="136" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:33</t>
         </is>
       </c>
     </row>
@@ -11917,7 +13431,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="128" t="inlineStr">
+      <c r="A1" s="134" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -11953,7 +13467,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="129" t="inlineStr">
+      <c r="A2" s="135" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -11986,9 +13500,9 @@
       <c r="AA2" s="74" t="n"/>
       <c r="AB2" s="74" t="n"/>
       <c r="AC2" s="75" t="n"/>
-      <c r="AD2" s="130" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:53</t>
+      <c r="AD2" s="136" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:33</t>
         </is>
       </c>
     </row>
@@ -13952,7 +15466,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="128" t="inlineStr">
+      <c r="A1" s="134" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -13966,7 +15480,7 @@
       <c r="H1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="129" t="inlineStr">
+      <c r="A2" s="135" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -13977,9 +15491,9 @@
       <c r="E2" s="74" t="n"/>
       <c r="F2" s="74" t="n"/>
       <c r="G2" s="75" t="n"/>
-      <c r="H2" s="130" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:54</t>
+      <c r="H2" s="136" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:33</t>
         </is>
       </c>
     </row>
@@ -15598,7 +17112,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="128" t="inlineStr">
+      <c r="A1" s="134" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -15611,7 +17125,7 @@
       <c r="G1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="129" t="inlineStr">
+      <c r="A2" s="135" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -15621,9 +17135,9 @@
       <c r="D2" s="74" t="n"/>
       <c r="E2" s="74" t="n"/>
       <c r="F2" s="75" t="n"/>
-      <c r="G2" s="130" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:54</t>
+      <c r="G2" s="136" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:33</t>
         </is>
       </c>
     </row>
@@ -16806,7 +18320,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="128" t="inlineStr">
+      <c r="A1" s="134" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -16818,7 +18332,7 @@
       <c r="F1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="129" t="inlineStr">
+      <c r="A2" s="135" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -16827,9 +18341,9 @@
       <c r="C2" s="74" t="n"/>
       <c r="D2" s="74" t="n"/>
       <c r="E2" s="75" t="n"/>
-      <c r="F2" s="130" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:54</t>
+      <c r="F2" s="136" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:33</t>
         </is>
       </c>
     </row>
@@ -17881,7 +19395,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="128" t="inlineStr">
+      <c r="A1" s="134" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -17917,7 +19431,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="129" t="inlineStr">
+      <c r="A2" s="135" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -17950,9 +19464,9 @@
       <c r="AA2" s="74" t="n"/>
       <c r="AB2" s="74" t="n"/>
       <c r="AC2" s="75" t="n"/>
-      <c r="AD2" s="130" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:54</t>
+      <c r="AD2" s="136" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:33</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
@@ -295,7 +295,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -434,11 +434,40 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
@@ -864,6 +893,17 @@
     <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4797,19 +4837,19 @@
     <col width="9" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="28" customWidth="1" style="97" min="22" max="22"/>
-    <col width="8" customWidth="1" style="97" min="23" max="23"/>
-    <col width="12" customWidth="1" style="97" min="24" max="24"/>
-    <col width="14" customWidth="1" style="97" min="25" max="25"/>
-    <col width="8" customWidth="1" style="97" min="26" max="27"/>
-    <col width="13" customWidth="1" style="97" min="27" max="27"/>
-    <col width="8" customWidth="1" style="97" min="28" max="28"/>
+    <col width="7" customWidth="1" style="97" min="23" max="23"/>
+    <col width="7" customWidth="1" style="97" min="24" max="24"/>
+    <col width="7" customWidth="1" style="97" min="25" max="25"/>
+    <col width="7" customWidth="1" style="97" min="26" max="27"/>
+    <col width="7" customWidth="1" style="97" min="27" max="27"/>
+    <col width="7" customWidth="1" style="97" min="28" max="28"/>
     <col width="12" customWidth="1" style="97" min="29" max="29"/>
     <col width="12" customWidth="1" style="97" min="30" max="30"/>
     <col width="12" customWidth="1" style="97" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="134" t="inlineStr">
+      <c r="A1" s="137" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -4845,7 +4885,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="135" t="inlineStr">
+      <c r="A2" s="138" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -4875,14 +4915,14 @@
       <c r="X2" s="74" t="n"/>
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
-      <c r="AA2" s="74" t="n"/>
-      <c r="AB2" s="74" t="n"/>
-      <c r="AC2" s="75" t="n"/>
-      <c r="AD2" s="136" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:33</t>
-        </is>
-      </c>
+      <c r="AA2" s="75" t="n"/>
+      <c r="AB2" s="139" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:56</t>
+        </is>
+      </c>
+      <c r="AC2" s="140" t="n"/>
+      <c r="AD2" s="141" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">
@@ -5156,12 +5196,14 @@
       </c>
       <c r="X4" s="49" t="inlineStr">
         <is>
-          <t>전장설계팀</t>
+          <t>전장설계
+팀</t>
         </is>
       </c>
       <c r="Y4" s="49" t="inlineStr">
         <is>
-          <t>소프트웨어팀</t>
+          <t>소프트웨
+어팀</t>
         </is>
       </c>
       <c r="Z4" s="49" t="inlineStr">
@@ -5171,7 +5213,8 @@
       </c>
       <c r="AA4" s="49" t="inlineStr">
         <is>
-          <t>제조기술2팀</t>
+          <t>제조기술
+2팀</t>
         </is>
       </c>
       <c r="AB4" s="49" t="inlineStr">
@@ -8315,9 +8358,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:AC2"/>
+  <mergeCells count="3">
+    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:AA2"/>
   </mergeCells>
   <dataValidations count="11">
     <dataValidation sqref="H5:H57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
@@ -8384,27 +8428,27 @@
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="14"/>
     <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="19"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="24"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="17" max="19"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="24"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="9" customWidth="1" min="25" max="25"/>
     <col width="10" customWidth="1" min="26" max="26"/>
     <col width="12" customWidth="1" min="27" max="28"/>
     <col width="12" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="30"/>
     <col width="8" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="31" max="31"/>
-    <col width="13" customWidth="1" min="32" max="34"/>
-    <col width="13" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
-    <col width="13" customWidth="1" min="35" max="39"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="34"/>
+    <col width="10" customWidth="1" min="33" max="33"/>
+    <col width="10" customWidth="1" min="34" max="34"/>
+    <col width="10" customWidth="1" min="35" max="39"/>
     <col width="8" customWidth="1" min="36" max="36"/>
     <col width="8" customWidth="1" min="37" max="37"/>
     <col width="8" customWidth="1" min="38" max="38"/>
@@ -8420,7 +8464,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="134" t="inlineStr">
+      <c r="A1" s="137" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -8469,7 +8513,7 @@
       <c r="AQ1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="135" t="inlineStr">
+      <c r="A2" s="138" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 진행현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -8512,15 +8556,15 @@
       <c r="AK2" s="74" t="n"/>
       <c r="AL2" s="74" t="n"/>
       <c r="AM2" s="74" t="n"/>
-      <c r="AN2" s="74" t="n"/>
-      <c r="AO2" s="74" t="n"/>
-      <c r="AP2" s="75" t="n"/>
-      <c r="AQ2" s="136" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:33</t>
-        </is>
-      </c>
-      <c r="AU2" s="133" t="inlineStr">
+      <c r="AN2" s="75" t="n"/>
+      <c r="AO2" s="139" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:56</t>
+        </is>
+      </c>
+      <c r="AP2" s="140" t="n"/>
+      <c r="AQ2" s="141" t="n"/>
+      <c r="AU2" s="136" t="inlineStr">
         <is>
           <t>업데이트: 2026-05-02 01:42</t>
         </is>
@@ -8843,61 +8887,71 @@
       </c>
       <c r="O4" s="49" t="inlineStr">
         <is>
-          <t>전장설계팀
+          <t>전장설계
+팀
 기구검토</t>
         </is>
       </c>
       <c r="P4" s="49" t="inlineStr">
         <is>
-          <t>전장설계팀
+          <t>전장설계
+팀
 IO맵/리스트</t>
         </is>
       </c>
       <c r="Q4" s="49" t="inlineStr">
         <is>
-          <t>전장설계팀
+          <t>전장설계
+팀
 설계</t>
         </is>
       </c>
       <c r="R4" s="49" t="inlineStr">
         <is>
-          <t>전장설계팀
+          <t>전장설계
+팀
 BOM작성</t>
         </is>
       </c>
       <c r="S4" s="49" t="inlineStr">
         <is>
-          <t>전장설계팀
+          <t>전장설계
+팀
 소계</t>
         </is>
       </c>
       <c r="T4" s="49" t="inlineStr">
         <is>
-          <t>소프트웨어팀
+          <t>소프트웨
+어팀
 검토</t>
         </is>
       </c>
       <c r="U4" s="49" t="inlineStr">
         <is>
-          <t>소프트웨어팀
+          <t>소프트웨
+어팀
 프로그램</t>
         </is>
       </c>
       <c r="V4" s="49" t="inlineStr">
         <is>
-          <t>소프트웨어팀
+          <t>소프트웨
+어팀
 DRYRUN</t>
         </is>
       </c>
       <c r="W4" s="49" t="inlineStr">
         <is>
-          <t>소프트웨어팀
+          <t>소프트웨
+어팀
 AUTORUN</t>
         </is>
       </c>
       <c r="X4" s="49" t="inlineStr">
         <is>
-          <t>소프트웨어팀
+          <t>소프트웨
+어팀
 소계</t>
         </is>
       </c>
@@ -8939,31 +8993,36 @@
       </c>
       <c r="AE4" s="49" t="inlineStr">
         <is>
-          <t>제조기술2팀
+          <t>제조기술
+2팀
 조립</t>
         </is>
       </c>
       <c r="AF4" s="49" t="inlineStr">
         <is>
-          <t>제조기술2팀
+          <t>제조기술
+2팀
 전장</t>
         </is>
       </c>
       <c r="AG4" s="49" t="inlineStr">
         <is>
-          <t>제조기술2팀
+          <t>제조기술
+2팀
 TURN-ON</t>
         </is>
       </c>
       <c r="AH4" s="49" t="inlineStr">
         <is>
-          <t>제조기술2팀
+          <t>제조기술
+2팀
 IO체크</t>
         </is>
       </c>
       <c r="AI4" s="49" t="inlineStr">
         <is>
-          <t>제조기술2팀
+          <t>제조기술
+2팀
 소계</t>
         </is>
       </c>
@@ -12281,9 +12340,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:AQ1"/>
-    <mergeCell ref="A2:AP2"/>
+    <mergeCell ref="A2:AN2"/>
+    <mergeCell ref="AO2:AQ2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -12326,7 +12386,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="134" t="inlineStr">
+      <c r="A1" s="137" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -12355,7 +12415,7 @@
       <c r="W1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="135" t="inlineStr">
+      <c r="A2" s="138" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -12378,14 +12438,14 @@
       <c r="Q2" s="74" t="n"/>
       <c r="R2" s="74" t="n"/>
       <c r="S2" s="74" t="n"/>
-      <c r="T2" s="74" t="n"/>
-      <c r="U2" s="74" t="n"/>
-      <c r="V2" s="75" t="n"/>
-      <c r="W2" s="136" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:33</t>
-        </is>
-      </c>
+      <c r="T2" s="75" t="n"/>
+      <c r="U2" s="139" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:56</t>
+        </is>
+      </c>
+      <c r="V2" s="140" t="n"/>
+      <c r="W2" s="141" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">
@@ -13378,9 +13438,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:V2"/>
+  <mergeCells count="3">
+    <mergeCell ref="U2:W2"/>
     <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A2:T2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -13419,19 +13480,19 @@
     <col width="9" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="28" customWidth="1" style="97" min="22" max="22"/>
-    <col width="8" customWidth="1" style="97" min="23" max="23"/>
-    <col width="12" customWidth="1" style="97" min="24" max="24"/>
-    <col width="14" customWidth="1" style="97" min="25" max="25"/>
-    <col width="8" customWidth="1" style="97" min="26" max="27"/>
-    <col width="13" customWidth="1" style="97" min="27" max="27"/>
-    <col width="8" customWidth="1" style="97" min="28" max="28"/>
+    <col width="7" customWidth="1" style="97" min="23" max="23"/>
+    <col width="7" customWidth="1" style="97" min="24" max="24"/>
+    <col width="7" customWidth="1" style="97" min="25" max="25"/>
+    <col width="7" customWidth="1" style="97" min="26" max="27"/>
+    <col width="7" customWidth="1" style="97" min="27" max="27"/>
+    <col width="7" customWidth="1" style="97" min="28" max="28"/>
     <col width="12" customWidth="1" style="97" min="29" max="29"/>
     <col width="12" customWidth="1" style="97" min="30" max="30"/>
     <col width="12" customWidth="1" style="97" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="134" t="inlineStr">
+      <c r="A1" s="137" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -13467,7 +13528,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="135" t="inlineStr">
+      <c r="A2" s="138" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -13497,14 +13558,14 @@
       <c r="X2" s="74" t="n"/>
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
-      <c r="AA2" s="74" t="n"/>
-      <c r="AB2" s="74" t="n"/>
-      <c r="AC2" s="75" t="n"/>
-      <c r="AD2" s="136" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:33</t>
-        </is>
-      </c>
+      <c r="AA2" s="75" t="n"/>
+      <c r="AB2" s="139" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:56</t>
+        </is>
+      </c>
+      <c r="AC2" s="140" t="n"/>
+      <c r="AD2" s="141" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">
@@ -13778,12 +13839,14 @@
       </c>
       <c r="X4" s="49" t="inlineStr">
         <is>
-          <t>전장설계팀</t>
+          <t>전장설계
+팀</t>
         </is>
       </c>
       <c r="Y4" s="49" t="inlineStr">
         <is>
-          <t>소프트웨어팀</t>
+          <t>소프트웨
+어팀</t>
         </is>
       </c>
       <c r="Z4" s="49" t="inlineStr">
@@ -13793,7 +13856,8 @@
       </c>
       <c r="AA4" s="49" t="inlineStr">
         <is>
-          <t>제조기술2팀</t>
+          <t>제조기술
+2팀</t>
         </is>
       </c>
       <c r="AB4" s="49" t="inlineStr">
@@ -15401,9 +15465,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:AC2"/>
+  <mergeCells count="3">
+    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:AA2"/>
   </mergeCells>
   <dataValidations count="11">
     <dataValidation sqref="H5:H41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">
@@ -15466,7 +15531,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="134" t="inlineStr">
+      <c r="A1" s="137" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -15480,7 +15545,7 @@
       <c r="H1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="135" t="inlineStr">
+      <c r="A2" s="138" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -15488,14 +15553,14 @@
       <c r="B2" s="74" t="n"/>
       <c r="C2" s="74" t="n"/>
       <c r="D2" s="74" t="n"/>
-      <c r="E2" s="74" t="n"/>
-      <c r="F2" s="74" t="n"/>
-      <c r="G2" s="75" t="n"/>
-      <c r="H2" s="136" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:33</t>
-        </is>
-      </c>
+      <c r="E2" s="75" t="n"/>
+      <c r="F2" s="139" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:56</t>
+        </is>
+      </c>
+      <c r="G2" s="140" t="n"/>
+      <c r="H2" s="141" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">
@@ -17083,8 +17148,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="F2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17112,7 +17178,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="134" t="inlineStr">
+      <c r="A1" s="137" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -17125,21 +17191,21 @@
       <c r="G1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="135" t="inlineStr">
+      <c r="A2" s="138" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
       </c>
       <c r="B2" s="74" t="n"/>
       <c r="C2" s="74" t="n"/>
-      <c r="D2" s="74" t="n"/>
-      <c r="E2" s="74" t="n"/>
-      <c r="F2" s="75" t="n"/>
-      <c r="G2" s="136" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:33</t>
-        </is>
-      </c>
+      <c r="D2" s="75" t="n"/>
+      <c r="E2" s="139" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:56</t>
+        </is>
+      </c>
+      <c r="F2" s="140" t="n"/>
+      <c r="G2" s="141" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">
@@ -18292,9 +18358,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
+  <mergeCells count="3">
+    <mergeCell ref="E2:G2"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -18320,7 +18387,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="134" t="inlineStr">
+      <c r="A1" s="137" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -18332,20 +18399,20 @@
       <c r="F1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="135" t="inlineStr">
+      <c r="A2" s="138" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
       </c>
       <c r="B2" s="74" t="n"/>
-      <c r="C2" s="74" t="n"/>
-      <c r="D2" s="74" t="n"/>
-      <c r="E2" s="75" t="n"/>
-      <c r="F2" s="136" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:33</t>
-        </is>
-      </c>
+      <c r="C2" s="75" t="n"/>
+      <c r="D2" s="139" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:56</t>
+        </is>
+      </c>
+      <c r="E2" s="140" t="n"/>
+      <c r="F2" s="141" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">
@@ -19343,9 +19410,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
+  <mergeCells count="3">
+    <mergeCell ref="D2:F2"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -19383,19 +19451,19 @@
     <col width="9" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="28" customWidth="1" style="97" min="22" max="22"/>
-    <col width="8" customWidth="1" style="97" min="23" max="23"/>
-    <col width="12" customWidth="1" style="97" min="24" max="24"/>
-    <col width="14" customWidth="1" style="97" min="25" max="25"/>
-    <col width="8" customWidth="1" style="97" min="26" max="26"/>
-    <col width="13" customWidth="1" style="97" min="27" max="27"/>
-    <col width="8" customWidth="1" style="97" min="28" max="28"/>
+    <col width="7" customWidth="1" style="97" min="23" max="23"/>
+    <col width="7" customWidth="1" style="97" min="24" max="24"/>
+    <col width="7" customWidth="1" style="97" min="25" max="25"/>
+    <col width="7" customWidth="1" style="97" min="26" max="26"/>
+    <col width="7" customWidth="1" style="97" min="27" max="27"/>
+    <col width="7" customWidth="1" style="97" min="28" max="28"/>
     <col width="12" customWidth="1" style="97" min="29" max="29"/>
     <col width="12" customWidth="1" style="97" min="30" max="30"/>
     <col width="12" customWidth="1" style="97" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="134" t="inlineStr">
+      <c r="A1" s="137" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -19431,7 +19499,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="135" t="inlineStr">
+      <c r="A2" s="138" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -19461,14 +19529,14 @@
       <c r="X2" s="74" t="n"/>
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
-      <c r="AA2" s="74" t="n"/>
-      <c r="AB2" s="74" t="n"/>
-      <c r="AC2" s="75" t="n"/>
-      <c r="AD2" s="136" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:33</t>
-        </is>
-      </c>
+      <c r="AA2" s="75" t="n"/>
+      <c r="AB2" s="139" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:56</t>
+        </is>
+      </c>
+      <c r="AC2" s="140" t="n"/>
+      <c r="AD2" s="141" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">
@@ -19742,12 +19810,14 @@
       </c>
       <c r="X4" s="49" t="inlineStr">
         <is>
-          <t>전장설계팀</t>
+          <t>전장설계
+팀</t>
         </is>
       </c>
       <c r="Y4" s="49" t="inlineStr">
         <is>
-          <t>소프트웨어팀</t>
+          <t>소프트웨
+어팀</t>
         </is>
       </c>
       <c r="Z4" s="49" t="inlineStr">
@@ -19757,7 +19827,8 @@
       </c>
       <c r="AA4" s="49" t="inlineStr">
         <is>
-          <t>제조기술2팀</t>
+          <t>제조기술
+2팀</t>
         </is>
       </c>
       <c r="AB4" s="49" t="inlineStr">
@@ -20739,9 +20810,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DEDA"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:AC2"/>
+  <mergeCells count="3">
+    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:AA2"/>
   </mergeCells>
   <dataValidations count="11">
     <dataValidation sqref="H5:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
@@ -467,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
@@ -904,6 +904,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -988,30 +997,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -1025,102 +1019,54 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사담당자 (고객사 PIC)
+        <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -1131,19 +1077,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -1158,170 +1096,90 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 담당영업 (영업 담당자)
+        <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PM (Project Manager)
+        <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수량
+        <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 통화 (KRW / USD)
+        <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 단가 (계약 단가)
+        <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 금액 (계약 총액)
+        <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주일 (공식 수주 일자)
+        <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 납기일 (납품 약속일)
+        <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
-        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 출하경로 (물류 루트)
+        <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 전체 진척률 (%)
+        <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -1331,312 +1189,184 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
-        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ D-day (납기 카운터)
+        <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
-        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 비고 (자유 메모)
+        <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
-        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 계산서
-발행일 (세부항목 진척률)
+        <t>▣ 계산서발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 입금일 (세부항목 진척률)
+        <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="F22" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R22)
+        <t>★ 권위 행 (R22)
 관리코드 003M2509의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="G22" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R22)
+        <t>★ 권위 행 (R22)
 관리코드 003M2509의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="F23" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 003M2509 모델 불일치
+        <t>⚠️ 관리코드 003M2509 모델 불일치
 권위(R22): Display 압착 자동화설비
 현재(R23): 지문센서조립 자동화 설비
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="G23" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 003M2509 품명 불일치
+        <t>⚠️ 관리코드 003M2509 품명 불일치
 권위(R22): BATTPRESSAUTO-S-V2
 현재(R23): FINGERASSY-S-V1
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="F24" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 003M2509 모델 불일치
+        <t>⚠️ 관리코드 003M2509 모델 불일치
 권위(R22): Display 압착 자동화설비
 현재(R24): 지문센서조립 자동화 설비
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="G24" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 003M2509 품명 불일치
+        <t>⚠️ 관리코드 003M2509 품명 불일치
 권위(R22): BATTPRESSAUTO-S-V2
 현재(R24): 지문센서 조립기 변위 센서 IL-100, IL-1000, OP-87056, 개조품DL-RS1A, 가공품
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -1651,30 +1381,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -1688,105 +1403,57 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 전체 진척률 (%)
+        <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -1796,736 +1463,423 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AE4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AF4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AG4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AH4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AI4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AJ4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AK4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AL4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AM4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AN4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AO4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AP4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AQ4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AR4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AS4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AT4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AU4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -2540,69 +1894,47 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 출하구분 (세부항목 진척률)
+        <t>▣ 출하구분 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ INV번호
-(출하코드) (세부항목 진척률)
+        <t>▣ INV번호(출하코드) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2616,292 +1948,204 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 차수/경로 (세부항목 진척률)
+        <t>▣ 차수/경로 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 거래유형 (세부항목 진척률)
+        <t>▣ 거래유형 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 통관분류 (세부항목 진척률)
+        <t>▣ 통관분류 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 출하일 (세부항목 진척률)
+        <t>▣ 출하일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 통화 (KRW / USD)
+        <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 환율 (세부항목 진척률)
+        <t>▣ 환율 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수량
+        <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ BOX수 (세부항목 진척률)
+        <t>▣ BOX수 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 금액 (계약 총액)
+        <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 인보이스(USD) (세부항목 진척률)
+        <t>▣ 인보이스(USD) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 작업 상태
+        <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ VN입고일 (세부항목 진척률)
+        <t>▣ VN입고일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 전체 진척률 (%)
+        <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -2911,67 +2155,54 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
-        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 입고
-완료 (세부항목 진척률)
+        <t>▣ 입고완료 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 출하
-완료 (세부항목 진척률)
+        <t>▣ 출하완료 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 조달
-진행률 (세부항목 진척률)
+        <t>▣ 조달진행률 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
   </commentList>
@@ -2986,30 +2217,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -3023,102 +2239,54 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사담당자 (고객사 PIC)
+        <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -3129,19 +2297,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -3156,170 +2316,90 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 담당영업 (영업 담당자)
+        <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PM (Project Manager)
+        <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수량
+        <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 통화 (KRW / USD)
+        <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 단가 (계약 단가)
+        <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 금액 (계약 총액)
+        <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주일 (공식 수주 일자)
+        <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 납기일 (납품 약속일)
+        <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
-        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 출하경로 (물류 루트)
+        <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 전체 진척률 (%)
+        <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -3329,212 +2409,132 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
-        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ D-day (납기 카운터)
+        <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
-        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 비고 (자유 메모)
+        <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
-        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 계산서
-발행일 (세부항목 진척률)
+        <t>▣ 계산서발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 입금일 (세부항목 진척률)
+        <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
   </commentList>
@@ -3549,30 +2549,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -3586,110 +2571,61 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주일 (공식 수주 일자)
+        <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -3704,30 +2640,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -3741,96 +2662,65 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 발행일 (세부항목 진척률)
+        <t>▣ 발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 발행사유 (세부항목 진척률)
+        <t>▣ 발행사유 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
   </commentList>
@@ -3845,49 +2735,26 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -3901,58 +2768,38 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 생성일 (세부항목 진척률)
+        <t>▣ 생성일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
   </commentList>
@@ -3967,30 +2814,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -4004,102 +2836,54 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사담당자 (고객사 PIC)
+        <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -4110,19 +2894,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -4137,170 +2913,90 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 담당영업 (영업 담당자)
+        <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PM (Project Manager)
+        <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수량
+        <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 통화 (KRW / USD)
+        <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 단가 (계약 단가)
+        <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 금액 (계약 총액)
+        <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주일 (공식 수주 일자)
+        <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 납기일 (납품 약속일)
+        <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
-        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 출하경로 (물류 루트)
+        <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 전체 진척률 (%)
+        <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -4310,212 +3006,132 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
-        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ D-day (납기 카운터)
+        <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
-        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 비고 (자유 메모)
+        <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
-        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 계산서
-발행일 (세부항목 진척률)
+        <t>▣ 계산서발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 입금일 (세부항목 진척률)
+        <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
   </commentList>
@@ -4849,7 +3465,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="137" t="inlineStr">
+      <c r="A1" s="142" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -4885,7 +3501,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="138" t="inlineStr">
+      <c r="A2" s="143" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -4916,13 +3532,13 @@
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="75" t="n"/>
-      <c r="AB2" s="139" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:56</t>
-        </is>
-      </c>
-      <c r="AC2" s="140" t="n"/>
-      <c r="AD2" s="141" t="n"/>
+      <c r="AB2" s="144" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:26</t>
+        </is>
+      </c>
+      <c r="AC2" s="74" t="n"/>
+      <c r="AD2" s="75" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">
@@ -5295,7 +3911,7 @@
       <c r="N5" s="54" t="n">
         <v>56900000</v>
       </c>
-      <c r="O5" s="55" t="n">
+      <c r="O5" s="78" t="n">
         <v>227600000</v>
       </c>
       <c r="P5" s="56" t="inlineStr">
@@ -5310,7 +3926,7 @@
       </c>
       <c r="R5" s="51" t="n"/>
       <c r="S5" s="57" t="n">
-        <v>0.15</v>
+        <v>0.9</v>
       </c>
       <c r="T5" s="58" t="n">
         <v>16</v>
@@ -5395,7 +4011,7 @@
       <c r="N6" s="63" t="n">
         <v>75840000</v>
       </c>
-      <c r="O6" s="64" t="n">
+      <c r="O6" s="79" t="n">
         <v>75840000</v>
       </c>
       <c r="P6" s="65" t="inlineStr">
@@ -5410,7 +4026,7 @@
       </c>
       <c r="R6" s="60" t="n"/>
       <c r="S6" s="66" t="n">
-        <v>0.13</v>
+        <v>0.78</v>
       </c>
       <c r="T6" s="67" t="n">
         <v>13</v>
@@ -5491,7 +4107,7 @@
       <c r="N7" s="54" t="n">
         <v>230700000</v>
       </c>
-      <c r="O7" s="55" t="n">
+      <c r="O7" s="78" t="n">
         <v>1614900000</v>
       </c>
       <c r="P7" s="56" t="inlineStr">
@@ -5505,7 +4121,9 @@
         </is>
       </c>
       <c r="R7" s="51" t="n"/>
-      <c r="S7" s="57" t="n"/>
+      <c r="S7" s="57" t="n">
+        <v>0.4</v>
+      </c>
       <c r="T7" s="58" t="n">
         <v>12</v>
       </c>
@@ -5589,7 +4207,7 @@
       <c r="N8" s="63" t="n">
         <v>230700000</v>
       </c>
-      <c r="O8" s="64" t="n">
+      <c r="O8" s="79" t="n">
         <v>1614900000</v>
       </c>
       <c r="P8" s="65" t="inlineStr">
@@ -5687,7 +4305,7 @@
       <c r="N9" s="54" t="n">
         <v>26000000</v>
       </c>
-      <c r="O9" s="55" t="n">
+      <c r="O9" s="78" t="n">
         <v>104000000</v>
       </c>
       <c r="P9" s="56" t="inlineStr">
@@ -5781,7 +4399,7 @@
       <c r="N10" s="63" t="n">
         <v>230700000</v>
       </c>
-      <c r="O10" s="64" t="n">
+      <c r="O10" s="79" t="n">
         <v>1845600000</v>
       </c>
       <c r="P10" s="65" t="inlineStr">
@@ -5875,7 +4493,7 @@
       <c r="N11" s="54" t="n">
         <v>254500000</v>
       </c>
-      <c r="O11" s="55" t="n">
+      <c r="O11" s="78" t="n">
         <v>254500000</v>
       </c>
       <c r="P11" s="56" t="inlineStr">
@@ -5969,7 +4587,7 @@
       <c r="N12" s="63" t="n">
         <v>227700000</v>
       </c>
-      <c r="O12" s="64" t="n">
+      <c r="O12" s="79" t="n">
         <v>1138500000</v>
       </c>
       <c r="P12" s="65" t="inlineStr">
@@ -6063,7 +4681,7 @@
       <c r="N13" s="54" t="n">
         <v>230700000</v>
       </c>
-      <c r="O13" s="55" t="n">
+      <c r="O13" s="78" t="n">
         <v>1384200000</v>
       </c>
       <c r="P13" s="56" t="inlineStr">
@@ -6157,7 +4775,7 @@
       <c r="N14" s="63" t="n">
         <v>248900000</v>
       </c>
-      <c r="O14" s="64" t="n">
+      <c r="O14" s="79" t="n">
         <v>995600000</v>
       </c>
       <c r="P14" s="65" t="inlineStr">
@@ -6251,7 +4869,7 @@
       <c r="N15" s="54" t="n">
         <v>248900000</v>
       </c>
-      <c r="O15" s="55" t="n">
+      <c r="O15" s="78" t="n">
         <v>746700000</v>
       </c>
       <c r="P15" s="56" t="inlineStr">
@@ -6345,7 +4963,7 @@
       <c r="N16" s="63" t="n">
         <v>65810000</v>
       </c>
-      <c r="O16" s="64" t="n">
+      <c r="O16" s="79" t="n">
         <v>131620000</v>
       </c>
       <c r="P16" s="65" t="inlineStr">
@@ -6441,7 +5059,7 @@
       <c r="N17" s="54" t="n">
         <v>59750000</v>
       </c>
-      <c r="O17" s="55" t="n">
+      <c r="O17" s="78" t="n">
         <v>119500000</v>
       </c>
       <c r="P17" s="56" t="inlineStr">
@@ -6537,7 +5155,7 @@
       <c r="N18" s="63" t="n">
         <v>59290000</v>
       </c>
-      <c r="O18" s="64" t="n">
+      <c r="O18" s="79" t="n">
         <v>59290000</v>
       </c>
       <c r="P18" s="65" t="inlineStr">
@@ -6629,7 +5247,7 @@
       <c r="N19" s="54" t="n">
         <v>26000000</v>
       </c>
-      <c r="O19" s="55" t="n">
+      <c r="O19" s="78" t="n">
         <v>26000000</v>
       </c>
       <c r="P19" s="56" t="inlineStr">
@@ -6721,7 +5339,7 @@
       <c r="N20" s="63" t="n">
         <v>28000000</v>
       </c>
-      <c r="O20" s="64" t="n">
+      <c r="O20" s="79" t="n">
         <v>28000000</v>
       </c>
       <c r="P20" s="65" t="inlineStr">
@@ -6813,7 +5431,7 @@
       <c r="N21" s="54" t="n">
         <v>36010000</v>
       </c>
-      <c r="O21" s="55" t="n">
+      <c r="O21" s="78" t="n">
         <v>36010000</v>
       </c>
       <c r="P21" s="56" t="inlineStr">
@@ -6864,12 +5482,12 @@
         </is>
       </c>
       <c r="E22" s="60" t="n"/>
-      <c r="F22" s="61" t="inlineStr">
+      <c r="F22" s="108" t="inlineStr">
         <is>
           <t>Display 압착 자동화설비</t>
         </is>
       </c>
-      <c r="G22" s="61" t="inlineStr">
+      <c r="G22" s="108" t="inlineStr">
         <is>
           <t>BATTPRESSAUTO-S-V2</t>
         </is>
@@ -6905,7 +5523,7 @@
       <c r="N22" s="63" t="n">
         <v>25779</v>
       </c>
-      <c r="O22" s="64" t="n">
+      <c r="O22" s="79" t="n">
         <v>232011</v>
       </c>
       <c r="P22" s="65" t="inlineStr">
@@ -6956,12 +5574,12 @@
         </is>
       </c>
       <c r="E23" s="51" t="n"/>
-      <c r="F23" s="52" t="inlineStr">
+      <c r="F23" s="107" t="inlineStr">
         <is>
           <t>지문센서조립 자동화 설비</t>
         </is>
       </c>
-      <c r="G23" s="52" t="inlineStr">
+      <c r="G23" s="107" t="inlineStr">
         <is>
           <t>FINGERASSY-S-V1</t>
         </is>
@@ -6997,7 +5615,7 @@
       <c r="N23" s="54" t="n">
         <v>49055</v>
       </c>
-      <c r="O23" s="55" t="n">
+      <c r="O23" s="78" t="n">
         <v>196220</v>
       </c>
       <c r="P23" s="56" t="inlineStr">
@@ -7048,12 +5666,12 @@
         </is>
       </c>
       <c r="E24" s="60" t="n"/>
-      <c r="F24" s="61" t="inlineStr">
+      <c r="F24" s="107" t="inlineStr">
         <is>
           <t>지문센서조립 자동화 설비</t>
         </is>
       </c>
-      <c r="G24" s="61" t="inlineStr">
+      <c r="G24" s="107" t="inlineStr">
         <is>
           <t>지문센서 조립기 변위 센서 IL-100, IL-1000, OP-87056, 개조품DL-RS1A, 가공품</t>
         </is>
@@ -7089,7 +5707,7 @@
       <c r="N24" s="63" t="n">
         <v>1480000</v>
       </c>
-      <c r="O24" s="64" t="n">
+      <c r="O24" s="79" t="n">
         <v>7400000</v>
       </c>
       <c r="P24" s="65" t="inlineStr">
@@ -7181,7 +5799,7 @@
       <c r="N25" s="54" t="n">
         <v>241900000</v>
       </c>
-      <c r="O25" s="55" t="n">
+      <c r="O25" s="78" t="n">
         <v>241900000</v>
       </c>
       <c r="P25" s="56" t="inlineStr">
@@ -7273,7 +5891,7 @@
       <c r="N26" s="63" t="n">
         <v>241900000</v>
       </c>
-      <c r="O26" s="64" t="n">
+      <c r="O26" s="79" t="n">
         <v>2902800000</v>
       </c>
       <c r="P26" s="65" t="inlineStr">
@@ -7365,7 +5983,7 @@
       <c r="N27" s="54" t="n">
         <v>98000000</v>
       </c>
-      <c r="O27" s="55" t="n">
+      <c r="O27" s="78" t="n">
         <v>98000000</v>
       </c>
       <c r="P27" s="56" t="inlineStr">
@@ -8464,7 +7082,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="137" t="inlineStr">
+      <c r="A1" s="142" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -8513,7 +7131,7 @@
       <c r="AQ1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="138" t="inlineStr">
+      <c r="A2" s="143" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 진행현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -8557,14 +7175,14 @@
       <c r="AL2" s="74" t="n"/>
       <c r="AM2" s="74" t="n"/>
       <c r="AN2" s="75" t="n"/>
-      <c r="AO2" s="139" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:56</t>
-        </is>
-      </c>
-      <c r="AP2" s="140" t="n"/>
-      <c r="AQ2" s="141" t="n"/>
-      <c r="AU2" s="136" t="inlineStr">
+      <c r="AO2" s="144" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:26</t>
+        </is>
+      </c>
+      <c r="AP2" s="74" t="n"/>
+      <c r="AQ2" s="75" t="n"/>
+      <c r="AU2" s="144" t="inlineStr">
         <is>
           <t>업데이트: 2026-05-02 01:42</t>
         </is>
@@ -9134,7 +7752,7 @@
         </is>
       </c>
       <c r="H5" s="57" t="n">
-        <v>0.15</v>
+        <v>0.9</v>
       </c>
       <c r="I5" s="57" t="n">
         <v>1</v>
@@ -9223,7 +7841,7 @@
         </is>
       </c>
       <c r="H6" s="66" t="n">
-        <v>0.13</v>
+        <v>0.78</v>
       </c>
       <c r="I6" s="66" t="n">
         <v>1</v>
@@ -9311,13 +7929,23 @@
           <t>진행중</t>
         </is>
       </c>
-      <c r="H7" s="57" t="n"/>
-      <c r="I7" s="57" t="n"/>
-      <c r="J7" s="57" t="n"/>
-      <c r="K7" s="57" t="n"/>
+      <c r="H7" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I7" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K7" s="57" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L7" s="57" t="n"/>
       <c r="M7" s="57" t="n"/>
-      <c r="N7" s="57" t="n"/>
+      <c r="N7" s="57" t="n">
+        <v>0.4</v>
+      </c>
       <c r="O7" s="57" t="n"/>
       <c r="P7" s="57" t="n"/>
       <c r="Q7" s="57" t="n"/>
@@ -9390,13 +8018,23 @@
           <t>진행중</t>
         </is>
       </c>
-      <c r="H8" s="66" t="n"/>
-      <c r="I8" s="66" t="n"/>
-      <c r="J8" s="66" t="n"/>
-      <c r="K8" s="66" t="n"/>
+      <c r="H8" s="66" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I8" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K8" s="66" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L8" s="66" t="n"/>
       <c r="M8" s="66" t="n"/>
-      <c r="N8" s="66" t="n"/>
+      <c r="N8" s="66" t="n">
+        <v>0.4</v>
+      </c>
       <c r="O8" s="66" t="n"/>
       <c r="P8" s="66" t="n"/>
       <c r="Q8" s="66" t="n"/>
@@ -9544,13 +8182,23 @@
           <t>진행중</t>
         </is>
       </c>
-      <c r="H10" s="66" t="n"/>
-      <c r="I10" s="66" t="n"/>
-      <c r="J10" s="66" t="n"/>
-      <c r="K10" s="66" t="n"/>
+      <c r="H10" s="66" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I10" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K10" s="66" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L10" s="66" t="n"/>
       <c r="M10" s="66" t="n"/>
-      <c r="N10" s="66" t="n"/>
+      <c r="N10" s="66" t="n">
+        <v>0.4</v>
+      </c>
       <c r="O10" s="66" t="n"/>
       <c r="P10" s="66" t="n"/>
       <c r="Q10" s="66" t="n"/>
@@ -9773,13 +8421,23 @@
           <t>진행중</t>
         </is>
       </c>
-      <c r="H13" s="57" t="n"/>
-      <c r="I13" s="57" t="n"/>
-      <c r="J13" s="57" t="n"/>
-      <c r="K13" s="57" t="n"/>
+      <c r="H13" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I13" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K13" s="57" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L13" s="57" t="n"/>
       <c r="M13" s="57" t="n"/>
-      <c r="N13" s="57" t="n"/>
+      <c r="N13" s="57" t="n">
+        <v>0.4</v>
+      </c>
       <c r="O13" s="57" t="n"/>
       <c r="P13" s="57" t="n"/>
       <c r="Q13" s="57" t="n"/>
@@ -12386,7 +11044,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="137" t="inlineStr">
+      <c r="A1" s="142" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -12415,7 +11073,7 @@
       <c r="W1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="138" t="inlineStr">
+      <c r="A2" s="143" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -12439,13 +11097,13 @@
       <c r="R2" s="74" t="n"/>
       <c r="S2" s="74" t="n"/>
       <c r="T2" s="75" t="n"/>
-      <c r="U2" s="139" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:56</t>
-        </is>
-      </c>
-      <c r="V2" s="140" t="n"/>
-      <c r="W2" s="141" t="n"/>
+      <c r="U2" s="144" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:26</t>
+        </is>
+      </c>
+      <c r="V2" s="74" t="n"/>
+      <c r="W2" s="75" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">
@@ -13492,7 +12150,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="137" t="inlineStr">
+      <c r="A1" s="142" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -13528,7 +12186,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="138" t="inlineStr">
+      <c r="A2" s="143" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -13559,13 +12217,13 @@
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="75" t="n"/>
-      <c r="AB2" s="139" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:56</t>
-        </is>
-      </c>
-      <c r="AC2" s="140" t="n"/>
-      <c r="AD2" s="141" t="n"/>
+      <c r="AB2" s="144" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:26</t>
+        </is>
+      </c>
+      <c r="AC2" s="74" t="n"/>
+      <c r="AD2" s="75" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">
@@ -15531,7 +14189,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="137" t="inlineStr">
+      <c r="A1" s="142" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -15545,7 +14203,7 @@
       <c r="H1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="138" t="inlineStr">
+      <c r="A2" s="143" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -15554,13 +14212,13 @@
       <c r="C2" s="74" t="n"/>
       <c r="D2" s="74" t="n"/>
       <c r="E2" s="75" t="n"/>
-      <c r="F2" s="139" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:56</t>
-        </is>
-      </c>
-      <c r="G2" s="140" t="n"/>
-      <c r="H2" s="141" t="n"/>
+      <c r="F2" s="144" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:26</t>
+        </is>
+      </c>
+      <c r="G2" s="74" t="n"/>
+      <c r="H2" s="75" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">
@@ -17178,7 +15836,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="137" t="inlineStr">
+      <c r="A1" s="142" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -17191,7 +15849,7 @@
       <c r="G1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="138" t="inlineStr">
+      <c r="A2" s="143" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -17199,13 +15857,13 @@
       <c r="B2" s="74" t="n"/>
       <c r="C2" s="74" t="n"/>
       <c r="D2" s="75" t="n"/>
-      <c r="E2" s="139" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:56</t>
-        </is>
-      </c>
-      <c r="F2" s="140" t="n"/>
-      <c r="G2" s="141" t="n"/>
+      <c r="E2" s="144" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:26</t>
+        </is>
+      </c>
+      <c r="F2" s="74" t="n"/>
+      <c r="G2" s="75" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">
@@ -18387,7 +17045,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="137" t="inlineStr">
+      <c r="A1" s="142" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -18399,20 +17057,20 @@
       <c r="F1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="138" t="inlineStr">
+      <c r="A2" s="143" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
       </c>
       <c r="B2" s="74" t="n"/>
       <c r="C2" s="75" t="n"/>
-      <c r="D2" s="139" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:56</t>
-        </is>
-      </c>
-      <c r="E2" s="140" t="n"/>
-      <c r="F2" s="141" t="n"/>
+      <c r="D2" s="144" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:27</t>
+        </is>
+      </c>
+      <c r="E2" s="74" t="n"/>
+      <c r="F2" s="75" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">
@@ -19463,7 +18121,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="137" t="inlineStr">
+      <c r="A1" s="142" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -19499,7 +18157,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="138" t="inlineStr">
+      <c r="A2" s="143" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -19530,13 +18188,13 @@
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="75" t="n"/>
-      <c r="AB2" s="139" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:56</t>
-        </is>
-      </c>
-      <c r="AC2" s="140" t="n"/>
-      <c r="AD2" s="141" t="n"/>
+      <c r="AB2" s="144" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:27</t>
+        </is>
+      </c>
+      <c r="AC2" s="74" t="n"/>
+      <c r="AD2" s="75" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="42" t="inlineStr">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
@@ -467,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
@@ -913,6 +913,15 @@
     <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -997,15 +1006,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -1019,54 +1043,102 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사담당자 (고객사 PIC)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -1077,11 +1149,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -1096,90 +1176,170 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당영업 (영업 담당자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PM (Project Manager)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수량
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통화 (KRW / USD)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 단가 (계약 단가)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 금액 (계약 총액)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주일 (공식 수주 일자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 납기일 (납품 약속일)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하경로 (물류 루트)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -1189,105 +1349,185 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ D-day (납기 카운터)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 비고 (자유 메모)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 계산서발행일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 계산서발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1299,11 +1539,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입금일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1315,58 +1563,107 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="F22" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R22)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R22)
 관리코드 003M2509의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="G22" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R22)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R22)
 관리코드 003M2509의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="F23" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 003M2509 모델 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 003M2509 모델 불일치
 권위(R22): Display 압착 자동화설비
 현재(R23): 지문센서조립 자동화 설비
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="G23" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 003M2509 품명 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 003M2509 품명 불일치
 권위(R22): BATTPRESSAUTO-S-V2
 현재(R23): FINGERASSY-S-V1
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="F24" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 003M2509 모델 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 003M2509 모델 불일치
 권위(R22): Display 압착 자동화설비
 현재(R24): 지문센서조립 자동화 설비
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="G24" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 003M2509 품명 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 003M2509 품명 불일치
 권위(R22): BATTPRESSAUTO-S-V2
 현재(R24): 지문센서 조립기 변위 센서 IL-100, IL-1000, OP-87056, 개조품DL-RS1A, 가공품
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1381,15 +1678,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -1403,57 +1715,105 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -1463,423 +1823,736 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AE4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AF4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AG4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AH4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AI4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AJ4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AK4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AL4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AM4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AN4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AO4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AP4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AQ4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AR4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AS4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AT4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AU4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1894,15 +2567,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하구분 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하구분 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1914,11 +2602,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ INV번호(출하코드) (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ INV번호(출하코드) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1930,11 +2626,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -1948,38 +2652,70 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 차수/경로 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 차수/경로 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1991,11 +2727,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 거래유형 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 거래유형 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2007,11 +2751,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통관분류 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통관분류 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2023,11 +2775,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2039,21 +2799,37 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통화 (KRW / USD)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 환율 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 환율 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2065,19 +2841,35 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수량
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ BOX수 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ BOX수 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2089,20 +2881,36 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 금액 (계약 총액)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 인보이스(USD) (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 인보이스(USD) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2114,22 +2922,38 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ VN입고일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ VN입고일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2141,11 +2965,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -2155,11 +2987,19 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입고완료 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입고완료 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2171,11 +3011,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하완료 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하완료 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2187,11 +3035,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 조달진행률 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 조달진행률 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2203,6 +3059,7 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2217,15 +3074,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2239,54 +3111,102 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사담당자 (고객사 PIC)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -2297,11 +3217,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -2316,90 +3244,170 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당영업 (영업 담당자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PM (Project Manager)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수량
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통화 (KRW / USD)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 단가 (계약 단가)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 금액 (계약 총액)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주일 (공식 수주 일자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 납기일 (납품 약속일)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하경로 (물류 루트)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -2409,105 +3417,185 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ D-day (납기 카운터)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 비고 (자유 메모)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 계산서발행일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 계산서발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2519,11 +3607,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입금일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2535,6 +3631,7 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2549,15 +3646,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2571,61 +3683,110 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주일 (공식 수주 일자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2640,15 +3801,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2662,38 +3838,70 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 발행일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2705,11 +3913,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 발행사유 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 발행사유 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2721,6 +3937,7 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2735,26 +3952,49 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2768,27 +4008,51 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 생성일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 생성일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2800,6 +4064,7 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2814,15 +4079,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2836,54 +4116,102 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사담당자 (고객사 PIC)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -2894,11 +4222,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -2913,90 +4249,170 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당영업 (영업 담당자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PM (Project Manager)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수량
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통화 (KRW / USD)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 단가 (계약 단가)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 금액 (계약 총액)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주일 (공식 수주 일자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 납기일 (납품 약속일)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하경로 (물류 루트)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -3006,105 +4422,185 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ D-day (납기 카운터)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 비고 (자유 메모)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 계산서발행일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 계산서발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -3116,11 +4612,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입금일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -3132,6 +4636,7 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -3465,7 +4970,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="142" t="inlineStr">
+      <c r="A1" s="145" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -3501,7 +5006,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="143" t="inlineStr">
+      <c r="A2" s="146" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -3532,9 +5037,9 @@
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="75" t="n"/>
-      <c r="AB2" s="144" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:26</t>
+      <c r="AB2" s="147" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:39</t>
         </is>
       </c>
       <c r="AC2" s="74" t="n"/>
@@ -3911,7 +5416,7 @@
       <c r="N5" s="54" t="n">
         <v>56900000</v>
       </c>
-      <c r="O5" s="78" t="n">
+      <c r="O5" s="55" t="n">
         <v>227600000</v>
       </c>
       <c r="P5" s="56" t="inlineStr">
@@ -4011,7 +5516,7 @@
       <c r="N6" s="63" t="n">
         <v>75840000</v>
       </c>
-      <c r="O6" s="79" t="n">
+      <c r="O6" s="64" t="n">
         <v>75840000</v>
       </c>
       <c r="P6" s="65" t="inlineStr">
@@ -4107,7 +5612,7 @@
       <c r="N7" s="54" t="n">
         <v>230700000</v>
       </c>
-      <c r="O7" s="78" t="n">
+      <c r="O7" s="55" t="n">
         <v>1614900000</v>
       </c>
       <c r="P7" s="56" t="inlineStr">
@@ -4207,7 +5712,7 @@
       <c r="N8" s="63" t="n">
         <v>230700000</v>
       </c>
-      <c r="O8" s="79" t="n">
+      <c r="O8" s="64" t="n">
         <v>1614900000</v>
       </c>
       <c r="P8" s="65" t="inlineStr">
@@ -4305,7 +5810,7 @@
       <c r="N9" s="54" t="n">
         <v>26000000</v>
       </c>
-      <c r="O9" s="78" t="n">
+      <c r="O9" s="55" t="n">
         <v>104000000</v>
       </c>
       <c r="P9" s="56" t="inlineStr">
@@ -4399,7 +5904,7 @@
       <c r="N10" s="63" t="n">
         <v>230700000</v>
       </c>
-      <c r="O10" s="79" t="n">
+      <c r="O10" s="64" t="n">
         <v>1845600000</v>
       </c>
       <c r="P10" s="65" t="inlineStr">
@@ -4493,7 +5998,7 @@
       <c r="N11" s="54" t="n">
         <v>254500000</v>
       </c>
-      <c r="O11" s="78" t="n">
+      <c r="O11" s="55" t="n">
         <v>254500000</v>
       </c>
       <c r="P11" s="56" t="inlineStr">
@@ -4587,7 +6092,7 @@
       <c r="N12" s="63" t="n">
         <v>227700000</v>
       </c>
-      <c r="O12" s="79" t="n">
+      <c r="O12" s="64" t="n">
         <v>1138500000</v>
       </c>
       <c r="P12" s="65" t="inlineStr">
@@ -4681,7 +6186,7 @@
       <c r="N13" s="54" t="n">
         <v>230700000</v>
       </c>
-      <c r="O13" s="78" t="n">
+      <c r="O13" s="55" t="n">
         <v>1384200000</v>
       </c>
       <c r="P13" s="56" t="inlineStr">
@@ -4775,7 +6280,7 @@
       <c r="N14" s="63" t="n">
         <v>248900000</v>
       </c>
-      <c r="O14" s="79" t="n">
+      <c r="O14" s="64" t="n">
         <v>995600000</v>
       </c>
       <c r="P14" s="65" t="inlineStr">
@@ -4869,7 +6374,7 @@
       <c r="N15" s="54" t="n">
         <v>248900000</v>
       </c>
-      <c r="O15" s="78" t="n">
+      <c r="O15" s="55" t="n">
         <v>746700000</v>
       </c>
       <c r="P15" s="56" t="inlineStr">
@@ -4963,7 +6468,7 @@
       <c r="N16" s="63" t="n">
         <v>65810000</v>
       </c>
-      <c r="O16" s="79" t="n">
+      <c r="O16" s="64" t="n">
         <v>131620000</v>
       </c>
       <c r="P16" s="65" t="inlineStr">
@@ -5059,7 +6564,7 @@
       <c r="N17" s="54" t="n">
         <v>59750000</v>
       </c>
-      <c r="O17" s="78" t="n">
+      <c r="O17" s="55" t="n">
         <v>119500000</v>
       </c>
       <c r="P17" s="56" t="inlineStr">
@@ -5155,7 +6660,7 @@
       <c r="N18" s="63" t="n">
         <v>59290000</v>
       </c>
-      <c r="O18" s="79" t="n">
+      <c r="O18" s="64" t="n">
         <v>59290000</v>
       </c>
       <c r="P18" s="65" t="inlineStr">
@@ -5247,7 +6752,7 @@
       <c r="N19" s="54" t="n">
         <v>26000000</v>
       </c>
-      <c r="O19" s="78" t="n">
+      <c r="O19" s="55" t="n">
         <v>26000000</v>
       </c>
       <c r="P19" s="56" t="inlineStr">
@@ -5339,7 +6844,7 @@
       <c r="N20" s="63" t="n">
         <v>28000000</v>
       </c>
-      <c r="O20" s="79" t="n">
+      <c r="O20" s="64" t="n">
         <v>28000000</v>
       </c>
       <c r="P20" s="65" t="inlineStr">
@@ -5431,7 +6936,7 @@
       <c r="N21" s="54" t="n">
         <v>36010000</v>
       </c>
-      <c r="O21" s="78" t="n">
+      <c r="O21" s="55" t="n">
         <v>36010000</v>
       </c>
       <c r="P21" s="56" t="inlineStr">
@@ -5482,12 +6987,12 @@
         </is>
       </c>
       <c r="E22" s="60" t="n"/>
-      <c r="F22" s="108" t="inlineStr">
+      <c r="F22" s="61" t="inlineStr">
         <is>
           <t>Display 압착 자동화설비</t>
         </is>
       </c>
-      <c r="G22" s="108" t="inlineStr">
+      <c r="G22" s="61" t="inlineStr">
         <is>
           <t>BATTPRESSAUTO-S-V2</t>
         </is>
@@ -5523,7 +7028,7 @@
       <c r="N22" s="63" t="n">
         <v>25779</v>
       </c>
-      <c r="O22" s="79" t="n">
+      <c r="O22" s="64" t="n">
         <v>232011</v>
       </c>
       <c r="P22" s="65" t="inlineStr">
@@ -5574,12 +7079,12 @@
         </is>
       </c>
       <c r="E23" s="51" t="n"/>
-      <c r="F23" s="107" t="inlineStr">
+      <c r="F23" s="52" t="inlineStr">
         <is>
           <t>지문센서조립 자동화 설비</t>
         </is>
       </c>
-      <c r="G23" s="107" t="inlineStr">
+      <c r="G23" s="52" t="inlineStr">
         <is>
           <t>FINGERASSY-S-V1</t>
         </is>
@@ -5615,7 +7120,7 @@
       <c r="N23" s="54" t="n">
         <v>49055</v>
       </c>
-      <c r="O23" s="78" t="n">
+      <c r="O23" s="55" t="n">
         <v>196220</v>
       </c>
       <c r="P23" s="56" t="inlineStr">
@@ -5666,12 +7171,12 @@
         </is>
       </c>
       <c r="E24" s="60" t="n"/>
-      <c r="F24" s="107" t="inlineStr">
+      <c r="F24" s="61" t="inlineStr">
         <is>
           <t>지문센서조립 자동화 설비</t>
         </is>
       </c>
-      <c r="G24" s="107" t="inlineStr">
+      <c r="G24" s="61" t="inlineStr">
         <is>
           <t>지문센서 조립기 변위 센서 IL-100, IL-1000, OP-87056, 개조품DL-RS1A, 가공품</t>
         </is>
@@ -5707,7 +7212,7 @@
       <c r="N24" s="63" t="n">
         <v>1480000</v>
       </c>
-      <c r="O24" s="79" t="n">
+      <c r="O24" s="64" t="n">
         <v>7400000</v>
       </c>
       <c r="P24" s="65" t="inlineStr">
@@ -5799,7 +7304,7 @@
       <c r="N25" s="54" t="n">
         <v>241900000</v>
       </c>
-      <c r="O25" s="78" t="n">
+      <c r="O25" s="55" t="n">
         <v>241900000</v>
       </c>
       <c r="P25" s="56" t="inlineStr">
@@ -5891,7 +7396,7 @@
       <c r="N26" s="63" t="n">
         <v>241900000</v>
       </c>
-      <c r="O26" s="79" t="n">
+      <c r="O26" s="64" t="n">
         <v>2902800000</v>
       </c>
       <c r="P26" s="65" t="inlineStr">
@@ -5983,7 +7488,7 @@
       <c r="N27" s="54" t="n">
         <v>98000000</v>
       </c>
-      <c r="O27" s="78" t="n">
+      <c r="O27" s="55" t="n">
         <v>98000000</v>
       </c>
       <c r="P27" s="56" t="inlineStr">
@@ -7082,7 +8587,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="142" t="inlineStr">
+      <c r="A1" s="145" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -7131,7 +8636,7 @@
       <c r="AQ1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="143" t="inlineStr">
+      <c r="A2" s="146" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 진행현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -7175,9 +8680,9 @@
       <c r="AL2" s="74" t="n"/>
       <c r="AM2" s="74" t="n"/>
       <c r="AN2" s="75" t="n"/>
-      <c r="AO2" s="144" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:26</t>
+      <c r="AO2" s="147" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:39</t>
         </is>
       </c>
       <c r="AP2" s="74" t="n"/>
@@ -11044,7 +12549,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="142" t="inlineStr">
+      <c r="A1" s="145" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -11073,7 +12578,7 @@
       <c r="W1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="143" t="inlineStr">
+      <c r="A2" s="146" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -11097,9 +12602,9 @@
       <c r="R2" s="74" t="n"/>
       <c r="S2" s="74" t="n"/>
       <c r="T2" s="75" t="n"/>
-      <c r="U2" s="144" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:26</t>
+      <c r="U2" s="147" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:39</t>
         </is>
       </c>
       <c r="V2" s="74" t="n"/>
@@ -12150,7 +13655,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="142" t="inlineStr">
+      <c r="A1" s="145" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -12186,7 +13691,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="143" t="inlineStr">
+      <c r="A2" s="146" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -12217,9 +13722,9 @@
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="75" t="n"/>
-      <c r="AB2" s="144" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:26</t>
+      <c r="AB2" s="147" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:39</t>
         </is>
       </c>
       <c r="AC2" s="74" t="n"/>
@@ -14189,7 +15694,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="142" t="inlineStr">
+      <c r="A1" s="145" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -14203,7 +15708,7 @@
       <c r="H1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="143" t="inlineStr">
+      <c r="A2" s="146" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -14212,9 +15717,9 @@
       <c r="C2" s="74" t="n"/>
       <c r="D2" s="74" t="n"/>
       <c r="E2" s="75" t="n"/>
-      <c r="F2" s="144" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:26</t>
+      <c r="F2" s="147" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:39</t>
         </is>
       </c>
       <c r="G2" s="74" t="n"/>
@@ -15836,7 +17341,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="142" t="inlineStr">
+      <c r="A1" s="145" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -15849,7 +17354,7 @@
       <c r="G1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="143" t="inlineStr">
+      <c r="A2" s="146" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -15857,9 +17362,9 @@
       <c r="B2" s="74" t="n"/>
       <c r="C2" s="74" t="n"/>
       <c r="D2" s="75" t="n"/>
-      <c r="E2" s="144" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:26</t>
+      <c r="E2" s="147" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:39</t>
         </is>
       </c>
       <c r="F2" s="74" t="n"/>
@@ -17045,7 +18550,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="142" t="inlineStr">
+      <c r="A1" s="145" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -17057,16 +18562,16 @@
       <c r="F1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="143" t="inlineStr">
+      <c r="A2" s="146" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
       </c>
       <c r="B2" s="74" t="n"/>
       <c r="C2" s="75" t="n"/>
-      <c r="D2" s="144" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:27</t>
+      <c r="D2" s="147" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:39</t>
         </is>
       </c>
       <c r="E2" s="74" t="n"/>
@@ -18121,7 +19626,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="142" t="inlineStr">
+      <c r="A1" s="145" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -18157,7 +19662,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="143" t="inlineStr">
+      <c r="A2" s="146" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -18188,9 +19693,9 @@
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="75" t="n"/>
-      <c r="AB2" s="144" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:27</t>
+      <c r="AB2" s="147" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:39</t>
         </is>
       </c>
       <c r="AC2" s="74" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
@@ -467,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
@@ -922,6 +922,15 @@
     <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1006,30 +1015,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -1043,102 +1037,54 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사담당자 (고객사 PIC)
+        <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -1149,19 +1095,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -1176,170 +1114,90 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 담당영업 (영업 담당자)
+        <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PM (Project Manager)
+        <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수량
+        <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 통화 (KRW / USD)
+        <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 단가 (계약 단가)
+        <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 금액 (계약 총액)
+        <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주일 (공식 수주 일자)
+        <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 납기일 (납품 약속일)
+        <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
-        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 출하경로 (물류 루트)
+        <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 전체 진척률 (%)
+        <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -1349,185 +1207,105 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
-        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ D-day (납기 카운터)
+        <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
-        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 비고 (자유 메모)
+        <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
-        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 계산서발행일 (세부항목 진척률)
+        <t>▣ 계산서발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1539,19 +1317,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 입금일 (세부항목 진척률)
+        <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1563,107 +1333,58 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="F22" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R22)
+        <t>★ 권위 행 (R22)
 관리코드 003M2509의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="G22" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>★ 권위 행 (R22)
+        <t>★ 권위 행 (R22)
 관리코드 003M2509의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
-        </r>
       </text>
     </comment>
     <comment ref="F23" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 003M2509 모델 불일치
+        <t>⚠️ 관리코드 003M2509 모델 불일치
 권위(R22): Display 압착 자동화설비
 현재(R23): 지문센서조립 자동화 설비
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="G23" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 003M2509 품명 불일치
+        <t>⚠️ 관리코드 003M2509 품명 불일치
 권위(R22): BATTPRESSAUTO-S-V2
 현재(R23): FINGERASSY-S-V1
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="F24" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 003M2509 모델 불일치
+        <t>⚠️ 관리코드 003M2509 모델 불일치
 권위(R22): Display 압착 자동화설비
 현재(R24): 지문센서조립 자동화 설비
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
     <comment ref="G24" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>⚠️ 관리코드 003M2509 품명 불일치
+        <t>⚠️ 관리코드 003M2509 품명 불일치
 권위(R22): BATTPRESSAUTO-S-V2
 현재(R24): 지문센서 조립기 변위 센서 IL-100, IL-1000, OP-87056, 개조품DL-RS1A, 가공품
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -1678,30 +1399,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -1715,105 +1421,57 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 전체 진척률 (%)
+        <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -1823,736 +1481,423 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AE4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AF4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AG4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AH4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AI4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AJ4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AK4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AL4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AM4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AN4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AO4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AP4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AQ4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AR4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AS4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AT4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AU4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -2567,30 +1912,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 출하구분 (세부항목 진척률)
+        <t>▣ 출하구분 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2602,19 +1932,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ INV번호(출하코드) (세부항목 진척률)
+        <t>▣ INV번호(출하코드) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2626,19 +1948,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2652,70 +1966,38 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 차수/경로 (세부항목 진척률)
+        <t>▣ 차수/경로 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2727,19 +2009,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 거래유형 (세부항목 진척률)
+        <t>▣ 거래유형 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2751,19 +2025,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 통관분류 (세부항목 진척률)
+        <t>▣ 통관분류 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2775,19 +2041,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 출하일 (세부항목 진척률)
+        <t>▣ 출하일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2799,37 +2057,21 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 통화 (KRW / USD)
+        <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 환율 (세부항목 진척률)
+        <t>▣ 환율 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2841,35 +2083,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수량
+        <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ BOX수 (세부항목 진척률)
+        <t>▣ BOX수 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2881,36 +2107,20 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 금액 (계약 총액)
+        <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 인보이스(USD) (세부항목 진척률)
+        <t>▣ 인보이스(USD) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2922,38 +2132,22 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 작업 상태
+        <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ VN입고일 (세부항목 진척률)
+        <t>▣ VN입고일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2965,19 +2159,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 전체 진척률 (%)
+        <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -2987,19 +2173,11 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
-        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 입고완료 (세부항목 진척률)
+        <t>▣ 입고완료 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -3011,19 +2189,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 출하완료 (세부항목 진척률)
+        <t>▣ 출하완료 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -3035,19 +2205,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 조달진행률 (세부항목 진척률)
+        <t>▣ 조달진행률 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -3059,7 +2221,6 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -3074,30 +2235,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -3111,102 +2257,54 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사담당자 (고객사 PIC)
+        <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -3217,19 +2315,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -3244,170 +2334,90 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 담당영업 (영업 담당자)
+        <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PM (Project Manager)
+        <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수량
+        <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 통화 (KRW / USD)
+        <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 단가 (계약 단가)
+        <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 금액 (계약 총액)
+        <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주일 (공식 수주 일자)
+        <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 납기일 (납품 약속일)
+        <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
-        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 출하경로 (물류 루트)
+        <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 전체 진척률 (%)
+        <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -3417,185 +2427,105 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
-        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ D-day (납기 카운터)
+        <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
-        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 비고 (자유 메모)
+        <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
-        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 계산서발행일 (세부항목 진척률)
+        <t>▣ 계산서발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -3607,19 +2537,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 입금일 (세부항목 진척률)
+        <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -3631,7 +2553,6 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -3646,30 +2567,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -3683,110 +2589,61 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주일 (공식 수주 일자)
+        <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -3801,30 +2658,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -3838,70 +2680,38 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 발행일 (세부항목 진척률)
+        <t>▣ 발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -3913,19 +2723,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 발행사유 (세부항목 진척률)
+        <t>▣ 발행사유 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -3937,7 +2739,6 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -3952,49 +2753,26 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -4008,51 +2786,27 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 생성일 (세부항목 진척률)
+        <t>▣ 생성일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -4064,7 +2818,6 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -4079,30 +2832,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -4116,102 +2854,54 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사담당자 (고객사 PIC)
+        <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -4222,19 +2912,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -4249,170 +2931,90 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 담당영업 (영업 담당자)
+        <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PM (Project Manager)
+        <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수량
+        <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 통화 (KRW / USD)
+        <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 단가 (계약 단가)
+        <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 금액 (계약 총액)
+        <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주일 (공식 수주 일자)
+        <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 납기일 (납품 약속일)
+        <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
-        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 출하경로 (물류 루트)
+        <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 전체 진척률 (%)
+        <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -4422,185 +3024,105 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
-        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ D-day (납기 카운터)
+        <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
-        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 비고 (자유 메모)
+        <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
-        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서담당자
+        <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
-        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 베트남 담당자
+        <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
-        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 계산서발행일 (세부항목 진척률)
+        <t>▣ 계산서발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -4612,19 +3134,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 입금일 (세부항목 진척률)
+        <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -4636,7 +3150,6 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -4970,7 +3483,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="145" t="inlineStr">
+      <c r="A1" s="148" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -5006,7 +3519,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="146" t="inlineStr">
+      <c r="A2" s="149" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -5037,9 +3550,9 @@
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="75" t="n"/>
-      <c r="AB2" s="147" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:39</t>
+      <c r="AB2" s="150" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:47</t>
         </is>
       </c>
       <c r="AC2" s="74" t="n"/>
@@ -5416,7 +3929,7 @@
       <c r="N5" s="54" t="n">
         <v>56900000</v>
       </c>
-      <c r="O5" s="55" t="n">
+      <c r="O5" s="78" t="n">
         <v>227600000</v>
       </c>
       <c r="P5" s="56" t="inlineStr">
@@ -5516,7 +4029,7 @@
       <c r="N6" s="63" t="n">
         <v>75840000</v>
       </c>
-      <c r="O6" s="64" t="n">
+      <c r="O6" s="79" t="n">
         <v>75840000</v>
       </c>
       <c r="P6" s="65" t="inlineStr">
@@ -5612,7 +4125,7 @@
       <c r="N7" s="54" t="n">
         <v>230700000</v>
       </c>
-      <c r="O7" s="55" t="n">
+      <c r="O7" s="78" t="n">
         <v>1614900000</v>
       </c>
       <c r="P7" s="56" t="inlineStr">
@@ -5712,7 +4225,7 @@
       <c r="N8" s="63" t="n">
         <v>230700000</v>
       </c>
-      <c r="O8" s="64" t="n">
+      <c r="O8" s="79" t="n">
         <v>1614900000</v>
       </c>
       <c r="P8" s="65" t="inlineStr">
@@ -5810,7 +4323,7 @@
       <c r="N9" s="54" t="n">
         <v>26000000</v>
       </c>
-      <c r="O9" s="55" t="n">
+      <c r="O9" s="78" t="n">
         <v>104000000</v>
       </c>
       <c r="P9" s="56" t="inlineStr">
@@ -5904,7 +4417,7 @@
       <c r="N10" s="63" t="n">
         <v>230700000</v>
       </c>
-      <c r="O10" s="64" t="n">
+      <c r="O10" s="79" t="n">
         <v>1845600000</v>
       </c>
       <c r="P10" s="65" t="inlineStr">
@@ -5998,7 +4511,7 @@
       <c r="N11" s="54" t="n">
         <v>254500000</v>
       </c>
-      <c r="O11" s="55" t="n">
+      <c r="O11" s="78" t="n">
         <v>254500000</v>
       </c>
       <c r="P11" s="56" t="inlineStr">
@@ -6092,7 +4605,7 @@
       <c r="N12" s="63" t="n">
         <v>227700000</v>
       </c>
-      <c r="O12" s="64" t="n">
+      <c r="O12" s="79" t="n">
         <v>1138500000</v>
       </c>
       <c r="P12" s="65" t="inlineStr">
@@ -6186,7 +4699,7 @@
       <c r="N13" s="54" t="n">
         <v>230700000</v>
       </c>
-      <c r="O13" s="55" t="n">
+      <c r="O13" s="78" t="n">
         <v>1384200000</v>
       </c>
       <c r="P13" s="56" t="inlineStr">
@@ -6280,7 +4793,7 @@
       <c r="N14" s="63" t="n">
         <v>248900000</v>
       </c>
-      <c r="O14" s="64" t="n">
+      <c r="O14" s="79" t="n">
         <v>995600000</v>
       </c>
       <c r="P14" s="65" t="inlineStr">
@@ -6374,7 +4887,7 @@
       <c r="N15" s="54" t="n">
         <v>248900000</v>
       </c>
-      <c r="O15" s="55" t="n">
+      <c r="O15" s="78" t="n">
         <v>746700000</v>
       </c>
       <c r="P15" s="56" t="inlineStr">
@@ -6468,7 +4981,7 @@
       <c r="N16" s="63" t="n">
         <v>65810000</v>
       </c>
-      <c r="O16" s="64" t="n">
+      <c r="O16" s="79" t="n">
         <v>131620000</v>
       </c>
       <c r="P16" s="65" t="inlineStr">
@@ -6564,7 +5077,7 @@
       <c r="N17" s="54" t="n">
         <v>59750000</v>
       </c>
-      <c r="O17" s="55" t="n">
+      <c r="O17" s="78" t="n">
         <v>119500000</v>
       </c>
       <c r="P17" s="56" t="inlineStr">
@@ -6660,7 +5173,7 @@
       <c r="N18" s="63" t="n">
         <v>59290000</v>
       </c>
-      <c r="O18" s="64" t="n">
+      <c r="O18" s="79" t="n">
         <v>59290000</v>
       </c>
       <c r="P18" s="65" t="inlineStr">
@@ -6752,7 +5265,7 @@
       <c r="N19" s="54" t="n">
         <v>26000000</v>
       </c>
-      <c r="O19" s="55" t="n">
+      <c r="O19" s="78" t="n">
         <v>26000000</v>
       </c>
       <c r="P19" s="56" t="inlineStr">
@@ -6844,7 +5357,7 @@
       <c r="N20" s="63" t="n">
         <v>28000000</v>
       </c>
-      <c r="O20" s="64" t="n">
+      <c r="O20" s="79" t="n">
         <v>28000000</v>
       </c>
       <c r="P20" s="65" t="inlineStr">
@@ -6936,7 +5449,7 @@
       <c r="N21" s="54" t="n">
         <v>36010000</v>
       </c>
-      <c r="O21" s="55" t="n">
+      <c r="O21" s="78" t="n">
         <v>36010000</v>
       </c>
       <c r="P21" s="56" t="inlineStr">
@@ -6987,12 +5500,12 @@
         </is>
       </c>
       <c r="E22" s="60" t="n"/>
-      <c r="F22" s="61" t="inlineStr">
+      <c r="F22" s="108" t="inlineStr">
         <is>
           <t>Display 압착 자동화설비</t>
         </is>
       </c>
-      <c r="G22" s="61" t="inlineStr">
+      <c r="G22" s="108" t="inlineStr">
         <is>
           <t>BATTPRESSAUTO-S-V2</t>
         </is>
@@ -7028,7 +5541,7 @@
       <c r="N22" s="63" t="n">
         <v>25779</v>
       </c>
-      <c r="O22" s="64" t="n">
+      <c r="O22" s="79" t="n">
         <v>232011</v>
       </c>
       <c r="P22" s="65" t="inlineStr">
@@ -7079,12 +5592,12 @@
         </is>
       </c>
       <c r="E23" s="51" t="n"/>
-      <c r="F23" s="52" t="inlineStr">
+      <c r="F23" s="107" t="inlineStr">
         <is>
           <t>지문센서조립 자동화 설비</t>
         </is>
       </c>
-      <c r="G23" s="52" t="inlineStr">
+      <c r="G23" s="107" t="inlineStr">
         <is>
           <t>FINGERASSY-S-V1</t>
         </is>
@@ -7120,7 +5633,7 @@
       <c r="N23" s="54" t="n">
         <v>49055</v>
       </c>
-      <c r="O23" s="55" t="n">
+      <c r="O23" s="78" t="n">
         <v>196220</v>
       </c>
       <c r="P23" s="56" t="inlineStr">
@@ -7171,12 +5684,12 @@
         </is>
       </c>
       <c r="E24" s="60" t="n"/>
-      <c r="F24" s="61" t="inlineStr">
+      <c r="F24" s="107" t="inlineStr">
         <is>
           <t>지문센서조립 자동화 설비</t>
         </is>
       </c>
-      <c r="G24" s="61" t="inlineStr">
+      <c r="G24" s="107" t="inlineStr">
         <is>
           <t>지문센서 조립기 변위 센서 IL-100, IL-1000, OP-87056, 개조품DL-RS1A, 가공품</t>
         </is>
@@ -7212,7 +5725,7 @@
       <c r="N24" s="63" t="n">
         <v>1480000</v>
       </c>
-      <c r="O24" s="64" t="n">
+      <c r="O24" s="79" t="n">
         <v>7400000</v>
       </c>
       <c r="P24" s="65" t="inlineStr">
@@ -7304,7 +5817,7 @@
       <c r="N25" s="54" t="n">
         <v>241900000</v>
       </c>
-      <c r="O25" s="55" t="n">
+      <c r="O25" s="78" t="n">
         <v>241900000</v>
       </c>
       <c r="P25" s="56" t="inlineStr">
@@ -7396,7 +5909,7 @@
       <c r="N26" s="63" t="n">
         <v>241900000</v>
       </c>
-      <c r="O26" s="64" t="n">
+      <c r="O26" s="79" t="n">
         <v>2902800000</v>
       </c>
       <c r="P26" s="65" t="inlineStr">
@@ -7488,7 +6001,7 @@
       <c r="N27" s="54" t="n">
         <v>98000000</v>
       </c>
-      <c r="O27" s="55" t="n">
+      <c r="O27" s="78" t="n">
         <v>98000000</v>
       </c>
       <c r="P27" s="56" t="inlineStr">
@@ -8587,7 +7100,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="145" t="inlineStr">
+      <c r="A1" s="148" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -8636,7 +7149,7 @@
       <c r="AQ1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="146" t="inlineStr">
+      <c r="A2" s="149" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 진행현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -8680,14 +7193,14 @@
       <c r="AL2" s="74" t="n"/>
       <c r="AM2" s="74" t="n"/>
       <c r="AN2" s="75" t="n"/>
-      <c r="AO2" s="147" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:39</t>
+      <c r="AO2" s="150" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:47</t>
         </is>
       </c>
       <c r="AP2" s="74" t="n"/>
       <c r="AQ2" s="75" t="n"/>
-      <c r="AU2" s="144" t="inlineStr">
+      <c r="AU2" s="150" t="inlineStr">
         <is>
           <t>업데이트: 2026-05-02 01:42</t>
         </is>
@@ -12549,7 +11062,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="145" t="inlineStr">
+      <c r="A1" s="148" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -12578,7 +11091,7 @@
       <c r="W1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="146" t="inlineStr">
+      <c r="A2" s="149" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -12602,9 +11115,9 @@
       <c r="R2" s="74" t="n"/>
       <c r="S2" s="74" t="n"/>
       <c r="T2" s="75" t="n"/>
-      <c r="U2" s="147" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:39</t>
+      <c r="U2" s="150" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:47</t>
         </is>
       </c>
       <c r="V2" s="74" t="n"/>
@@ -13655,7 +12168,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="145" t="inlineStr">
+      <c r="A1" s="148" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -13691,7 +12204,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="146" t="inlineStr">
+      <c r="A2" s="149" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -13722,9 +12235,9 @@
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="75" t="n"/>
-      <c r="AB2" s="147" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:39</t>
+      <c r="AB2" s="150" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:47</t>
         </is>
       </c>
       <c r="AC2" s="74" t="n"/>
@@ -15694,7 +14207,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="145" t="inlineStr">
+      <c r="A1" s="148" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -15708,7 +14221,7 @@
       <c r="H1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="146" t="inlineStr">
+      <c r="A2" s="149" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -15717,9 +14230,9 @@
       <c r="C2" s="74" t="n"/>
       <c r="D2" s="74" t="n"/>
       <c r="E2" s="75" t="n"/>
-      <c r="F2" s="147" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:39</t>
+      <c r="F2" s="150" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:47</t>
         </is>
       </c>
       <c r="G2" s="74" t="n"/>
@@ -17341,7 +15854,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="145" t="inlineStr">
+      <c r="A1" s="148" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -17354,7 +15867,7 @@
       <c r="G1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="146" t="inlineStr">
+      <c r="A2" s="149" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -17362,9 +15875,9 @@
       <c r="B2" s="74" t="n"/>
       <c r="C2" s="74" t="n"/>
       <c r="D2" s="75" t="n"/>
-      <c r="E2" s="147" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:39</t>
+      <c r="E2" s="150" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:47</t>
         </is>
       </c>
       <c r="F2" s="74" t="n"/>
@@ -18550,7 +17063,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="145" t="inlineStr">
+      <c r="A1" s="148" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -18562,16 +17075,16 @@
       <c r="F1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="146" t="inlineStr">
+      <c r="A2" s="149" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
       </c>
       <c r="B2" s="74" t="n"/>
       <c r="C2" s="75" t="n"/>
-      <c r="D2" s="147" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:39</t>
+      <c r="D2" s="150" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:47</t>
         </is>
       </c>
       <c r="E2" s="74" t="n"/>
@@ -19626,7 +18139,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="145" t="inlineStr">
+      <c r="A1" s="148" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -19662,7 +18175,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="146" t="inlineStr">
+      <c r="A2" s="149" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -19693,9 +18206,9 @@
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="75" t="n"/>
-      <c r="AB2" s="147" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:39</t>
+      <c r="AB2" s="150" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:47</t>
         </is>
       </c>
       <c r="AC2" s="74" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
@@ -467,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
@@ -931,6 +931,15 @@
     <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1015,15 +1024,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -1037,54 +1061,102 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사담당자 (고객사 PIC)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -1095,11 +1167,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -1114,90 +1194,170 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당영업 (영업 담당자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PM (Project Manager)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수량
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통화 (KRW / USD)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 단가 (계약 단가)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 금액 (계약 총액)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주일 (공식 수주 일자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 납기일 (납품 약속일)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하경로 (물류 루트)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -1207,105 +1367,185 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ D-day (납기 카운터)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 비고 (자유 메모)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 계산서발행일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 계산서발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1317,11 +1557,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입금일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1333,58 +1581,107 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="F22" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R22)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R22)
 관리코드 003M2509의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="G22" authorId="0" shapeId="0">
       <text>
-        <t>★ 권위 행 (R22)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>★ 권위 행 (R22)
 관리코드 003M2509의 기준값.
 같은 코드를 가진 다른 행(노랑)에서
 이 값과 비교됩니다.</t>
+        </r>
       </text>
     </comment>
     <comment ref="F23" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 003M2509 모델 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 003M2509 모델 불일치
 권위(R22): Display 압착 자동화설비
 현재(R23): 지문센서조립 자동화 설비
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="G23" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 003M2509 품명 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 003M2509 품명 불일치
 권위(R22): BATTPRESSAUTO-S-V2
 현재(R23): FINGERASSY-S-V1
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="F24" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 003M2509 모델 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 003M2509 모델 불일치
 권위(R22): Display 압착 자동화설비
 현재(R24): 지문센서조립 자동화 설비
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
     <comment ref="G24" authorId="0" shapeId="0">
       <text>
-        <t>⚠️ 관리코드 003M2509 품명 불일치
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>⚠️ 관리코드 003M2509 품명 불일치
 권위(R22): BATTPRESSAUTO-S-V2
 현재(R24): 지문센서 조립기 변위 센서 IL-100, IL-1000, OP-87056, 개조품DL-RS1A, 가공품
 같은 검사기면 → 위 권위 값으로 수정
 다른 검사기면 → 관리코드 비우고 sync 재실행 (새 코드 부여)</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1399,15 +1696,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -1421,57 +1733,105 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -1481,423 +1841,736 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AE4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AF4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AG4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AH4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AI4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AJ4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AK4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AL4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AM4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AN4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AO4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AP4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AQ4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AR4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AS4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AT4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AU4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1912,15 +2585,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하구분 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하구분 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1932,11 +2620,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ INV번호(출하코드) (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ INV번호(출하코드) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1948,11 +2644,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -1966,38 +2670,70 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 차수/경로 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 차수/경로 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2009,11 +2745,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 거래유형 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 거래유형 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2025,11 +2769,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통관분류 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통관분류 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2041,11 +2793,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2057,21 +2817,37 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통화 (KRW / USD)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 환율 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 환율 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2083,19 +2859,35 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수량
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ BOX수 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ BOX수 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2107,20 +2899,36 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 금액 (계약 총액)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 인보이스(USD) (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 인보이스(USD) (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2132,22 +2940,38 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ VN입고일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ VN입고일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2159,11 +2983,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -2173,11 +3005,19 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입고완료 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입고완료 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2189,11 +3029,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하완료 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하완료 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2205,11 +3053,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 조달진행률 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 조달진행률 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2221,6 +3077,7 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2235,15 +3092,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2257,54 +3129,102 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사담당자 (고객사 PIC)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -2315,11 +3235,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -2334,90 +3262,170 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당영업 (영업 담당자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PM (Project Manager)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수량
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통화 (KRW / USD)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 단가 (계약 단가)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 금액 (계약 총액)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주일 (공식 수주 일자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 납기일 (납품 약속일)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하경로 (물류 루트)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -2427,105 +3435,185 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ D-day (납기 카운터)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 비고 (자유 메모)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 계산서발행일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 계산서발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2537,11 +3625,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입금일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2553,6 +3649,7 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2567,15 +3664,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2589,61 +3701,110 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주일 (공식 수주 일자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2658,15 +3819,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2680,38 +3856,70 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 발행일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2723,11 +3931,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 발행사유 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 발행사유 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2739,6 +3955,7 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2753,26 +3970,49 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2786,27 +4026,51 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 생성일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 생성일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -2818,6 +4082,7 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2832,15 +4097,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -2854,54 +4134,102 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사담당자 (고객사 PIC)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사담당자 (고객사 PIC)
 • 고객사 측 담당자 이름 + 직책 직접 입력
 • 예: '장영남 수석', '김용우 책임'
 • 출하·납품·A/S 시 연락처로 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -2912,11 +4240,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -2931,90 +4267,170 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당영업 (영업 담당자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 담당영업 (영업 담당자)
 • 영업 인원 이름 직접 입력
 • 예: 이현, 오경환, 이해림, 안지연
 • 담당영업별 실적 집계 기준
 • 관리코드 미발행 건의 사업부 분류에도 사용</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PM (Project Manager)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PM (Project Manager)
 • 프로젝트 매니저 이름 직접 입력
 • 수주확정 후 PM이 지정되면 기입
 • 부서 간 조율·납기 관리 책임자</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수량
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수량
 • 숫자 입력 (중앙 정렬, 천단위 콤마)
 • 정수 또는 소수 허용
 • 금액 = 수량 × 단가 (sync 시 자동 계산)</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 통화 (KRW / USD)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 통화 (KRW / USD)
 • 드롭다운 — 수주 계약 통화
   KRW — 국내 거래 (원화)
   USD — 해외 거래 (베트남·수출)
 • 단가·금액 포맷이 통화에 따라 자동 변경
   KRW → ₩#,##0       USD → $#,##0.00</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 단가 (계약 단가)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 단가 (계약 단가)
 • 숫자 입력 (우측 정렬)
 • 통화별 포맷 자동 적용 (₩ 또는 $)
 • sync 시 금액(= 수량 × 단가) 자동 재계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 금액 (계약 총액)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 금액 (계약 총액)
 • 자동 계산 = 수량 × 단가
 • 수동 수정 잠김 — 수량·단가 변경 후 sync 재실행
 • 통화별 포맷 (₩ / $) 자동 적용
 • 대시보드 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주일 (공식 수주 일자)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주일 (공식 수주 일자)
 • 입력 YYYY-MM-DD  예: 2026-04-15
 • 허용 형식(모두 자동 정규화):
   2026/4/15, 2026.4.15, 260415, 20260415
 • 수주번호 생성·월별 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 납기일 (납품 약속일)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 납기일 (납품 약속일)
 • 입력 YYYY-MM-DD  예: 2026-08-31
 • 수주일과 동일한 허용 형식
 • D-day 자동 계산 기준
 • 정렬 기준 — 납기 임박한 건이 상단</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 출하경로 (물류 루트)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 출하경로 (물류 루트)
 • 드롭다운:
   K→고객사       — 한국 내 직접 납품
   K→V→K→고객사 — 한국→베트남→한국→고객사
   K→V→고객사    — 한국→베트남→고객사 (해외)</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률 (%)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 전체 진척률 (%)
 • 자동 계산 (수정 불가, sync 시 갱신)
 📌 사업부별 계산식:
   ▸ 01 검사기  = 완료 부서 수 / 참여 부서 수
@@ -3024,105 +4440,185 @@
 • '제외' 부서는 분모에서 빠짐
 • 100% = 전 참여 부서 완료
 • 부서 파일 '부서진척률(%)'은 본인 부서만의 값</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ D-day (납기 카운터)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ D-day (납기 카운터)
 • 자동 계산 = (오늘 - 납기일)
   음수 (-)  → 남은 일수 (예: -5일 = 5일 남음)
   0        → 오늘이 납기일
   양수 (+)  → 지연 일수 (예: +3일 = 3일 지남)
 • 납품완료/취소/보류 상태는 공란 처리</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 비고 (자유 메모)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 비고 (자유 메모)
 • 자유 텍스트 입력 (좌측 정렬)
 • 특이사항·요청사항·이슈 메모
 • 대시보드 집계에는 포함되지 않음</t>
+        </r>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 이 부서 미참여
      (해당 부서 파일에 프로젝트 안 올라감)
   2) 빈 칸 → 부서 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 부서 파일 자동 반영
 • 부서 파일에서 담당자 입력 시 PMS에 역반영</t>
+        </r>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 베트남 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 베트남 담당자
 • 3가지 입력 방식:
   1) '제외' 선택 → 베트남 미참여
   2) 빈 칸 → 베트남 참여 확정, 담당자 미정
   3) 담당자 이름 직접 입력 → 베트남 파일 자동 반영
 • 주로 해외 출하 / 현지 조립 프로젝트에 활용</t>
+        </r>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 계산서발행일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 계산서발행일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -3134,11 +4630,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입금일 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입금일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -3150,6 +4654,7 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -3483,7 +4988,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="148" t="inlineStr">
+      <c r="A1" s="151" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -3519,7 +5024,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="149" t="inlineStr">
+      <c r="A2" s="152" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -3550,9 +5055,9 @@
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="75" t="n"/>
-      <c r="AB2" s="150" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:47</t>
+      <c r="AB2" s="153" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:58</t>
         </is>
       </c>
       <c r="AC2" s="74" t="n"/>
@@ -7100,7 +8605,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="148" t="inlineStr">
+      <c r="A1" s="151" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -7149,7 +8654,7 @@
       <c r="AQ1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="149" t="inlineStr">
+      <c r="A2" s="152" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 진행현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -7193,14 +8698,14 @@
       <c r="AL2" s="74" t="n"/>
       <c r="AM2" s="74" t="n"/>
       <c r="AN2" s="75" t="n"/>
-      <c r="AO2" s="150" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:47</t>
+      <c r="AO2" s="153" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:59</t>
         </is>
       </c>
       <c r="AP2" s="74" t="n"/>
       <c r="AQ2" s="75" t="n"/>
-      <c r="AU2" s="150" t="inlineStr">
+      <c r="AU2" s="153" t="inlineStr">
         <is>
           <t>업데이트: 2026-05-02 01:42</t>
         </is>
@@ -11062,7 +12567,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="148" t="inlineStr">
+      <c r="A1" s="151" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -11091,7 +12596,7 @@
       <c r="W1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="149" t="inlineStr">
+      <c r="A2" s="152" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -11115,9 +12620,9 @@
       <c r="R2" s="74" t="n"/>
       <c r="S2" s="74" t="n"/>
       <c r="T2" s="75" t="n"/>
-      <c r="U2" s="150" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:47</t>
+      <c r="U2" s="153" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:59</t>
         </is>
       </c>
       <c r="V2" s="74" t="n"/>
@@ -12168,7 +13673,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="148" t="inlineStr">
+      <c r="A1" s="151" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -12204,7 +13709,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="149" t="inlineStr">
+      <c r="A2" s="152" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -12235,9 +13740,9 @@
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="75" t="n"/>
-      <c r="AB2" s="150" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:47</t>
+      <c r="AB2" s="153" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:59</t>
         </is>
       </c>
       <c r="AC2" s="74" t="n"/>
@@ -14207,7 +15712,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="148" t="inlineStr">
+      <c r="A1" s="151" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -14221,7 +15726,7 @@
       <c r="H1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="149" t="inlineStr">
+      <c r="A2" s="152" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -14230,9 +15735,9 @@
       <c r="C2" s="74" t="n"/>
       <c r="D2" s="74" t="n"/>
       <c r="E2" s="75" t="n"/>
-      <c r="F2" s="150" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:47</t>
+      <c r="F2" s="153" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:59</t>
         </is>
       </c>
       <c r="G2" s="74" t="n"/>
@@ -15854,7 +17359,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="148" t="inlineStr">
+      <c r="A1" s="151" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -15867,7 +17372,7 @@
       <c r="G1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="149" t="inlineStr">
+      <c r="A2" s="152" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -15875,9 +17380,9 @@
       <c r="B2" s="74" t="n"/>
       <c r="C2" s="74" t="n"/>
       <c r="D2" s="75" t="n"/>
-      <c r="E2" s="150" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:47</t>
+      <c r="E2" s="153" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:59</t>
         </is>
       </c>
       <c r="F2" s="74" t="n"/>
@@ -17063,7 +18568,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="148" t="inlineStr">
+      <c r="A1" s="151" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -17075,16 +18580,16 @@
       <c r="F1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="149" t="inlineStr">
+      <c r="A2" s="152" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
       </c>
       <c r="B2" s="74" t="n"/>
       <c r="C2" s="75" t="n"/>
-      <c r="D2" s="150" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:47</t>
+      <c r="D2" s="153" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:59</t>
         </is>
       </c>
       <c r="E2" s="74" t="n"/>
@@ -18139,7 +19644,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="148" t="inlineStr">
+      <c r="A1" s="151" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -18175,7 +19680,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="149" t="inlineStr">
+      <c r="A2" s="152" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -18206,9 +19711,9 @@
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="75" t="n"/>
-      <c r="AB2" s="150" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:47</t>
+      <c r="AB2" s="153" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 14:00</t>
         </is>
       </c>
       <c r="AC2" s="74" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
@@ -467,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
@@ -904,6 +904,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -4988,7 +5006,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="151" t="inlineStr">
+      <c r="A1" s="157" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -5024,7 +5042,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="152" t="inlineStr">
+      <c r="A2" s="158" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -5055,9 +5073,9 @@
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="75" t="n"/>
-      <c r="AB2" s="153" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:58</t>
+      <c r="AB2" s="159" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 14:34</t>
         </is>
       </c>
       <c r="AC2" s="74" t="n"/>
@@ -8605,7 +8623,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="151" t="inlineStr">
+      <c r="A1" s="157" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -8654,7 +8672,7 @@
       <c r="AQ1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="152" t="inlineStr">
+      <c r="A2" s="158" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 진행현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -8698,14 +8716,14 @@
       <c r="AL2" s="74" t="n"/>
       <c r="AM2" s="74" t="n"/>
       <c r="AN2" s="75" t="n"/>
-      <c r="AO2" s="153" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:59</t>
+      <c r="AO2" s="159" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 14:34</t>
         </is>
       </c>
       <c r="AP2" s="74" t="n"/>
       <c r="AQ2" s="75" t="n"/>
-      <c r="AU2" s="153" t="inlineStr">
+      <c r="AU2" s="159" t="inlineStr">
         <is>
           <t>업데이트: 2026-05-02 01:42</t>
         </is>
@@ -12567,7 +12585,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="151" t="inlineStr">
+      <c r="A1" s="157" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -12596,7 +12614,7 @@
       <c r="W1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="152" t="inlineStr">
+      <c r="A2" s="158" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -12620,9 +12638,9 @@
       <c r="R2" s="74" t="n"/>
       <c r="S2" s="74" t="n"/>
       <c r="T2" s="75" t="n"/>
-      <c r="U2" s="153" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:59</t>
+      <c r="U2" s="159" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 14:35</t>
         </is>
       </c>
       <c r="V2" s="74" t="n"/>
@@ -13673,7 +13691,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="151" t="inlineStr">
+      <c r="A1" s="157" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -13709,7 +13727,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="152" t="inlineStr">
+      <c r="A2" s="158" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -13740,9 +13758,9 @@
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="75" t="n"/>
-      <c r="AB2" s="153" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:59</t>
+      <c r="AB2" s="159" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 14:35</t>
         </is>
       </c>
       <c r="AC2" s="74" t="n"/>
@@ -15712,7 +15730,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="151" t="inlineStr">
+      <c r="A1" s="157" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -15726,7 +15744,7 @@
       <c r="H1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="152" t="inlineStr">
+      <c r="A2" s="158" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -15735,9 +15753,9 @@
       <c r="C2" s="74" t="n"/>
       <c r="D2" s="74" t="n"/>
       <c r="E2" s="75" t="n"/>
-      <c r="F2" s="153" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:59</t>
+      <c r="F2" s="159" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 14:35</t>
         </is>
       </c>
       <c r="G2" s="74" t="n"/>
@@ -17359,7 +17377,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="151" t="inlineStr">
+      <c r="A1" s="157" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -17372,7 +17390,7 @@
       <c r="G1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="152" t="inlineStr">
+      <c r="A2" s="158" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -17380,9 +17398,9 @@
       <c r="B2" s="74" t="n"/>
       <c r="C2" s="74" t="n"/>
       <c r="D2" s="75" t="n"/>
-      <c r="E2" s="153" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:59</t>
+      <c r="E2" s="159" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 14:35</t>
         </is>
       </c>
       <c r="F2" s="74" t="n"/>
@@ -18568,7 +18586,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="151" t="inlineStr">
+      <c r="A1" s="157" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -18580,16 +18598,16 @@
       <c r="F1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="152" t="inlineStr">
+      <c r="A2" s="158" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
       </c>
       <c r="B2" s="74" t="n"/>
       <c r="C2" s="75" t="n"/>
-      <c r="D2" s="153" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:59</t>
+      <c r="D2" s="159" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 14:35</t>
         </is>
       </c>
       <c r="E2" s="74" t="n"/>
@@ -19644,7 +19662,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="151" t="inlineStr">
+      <c r="A1" s="157" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -19680,7 +19698,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="152" t="inlineStr">
+      <c r="A2" s="158" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -19711,9 +19729,9 @@
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="75" t="n"/>
-      <c r="AB2" s="153" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 14:00</t>
+      <c r="AB2" s="159" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 14:35</t>
         </is>
       </c>
       <c r="AC2" s="74" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_PMS_2026.xlsx
@@ -467,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
@@ -904,6 +904,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -5006,7 +5015,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="157" t="inlineStr">
+      <c r="A1" s="160" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 프로젝트 등록 │ 2026</t>
         </is>
@@ -5042,7 +5051,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="158" t="inlineStr">
+      <c r="A2" s="161" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -5073,9 +5082,9 @@
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="75" t="n"/>
-      <c r="AB2" s="159" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 14:34</t>
+      <c r="AB2" s="162" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 15:14</t>
         </is>
       </c>
       <c r="AC2" s="74" t="n"/>
@@ -8623,7 +8632,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="157" t="inlineStr">
+      <c r="A1" s="160" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 진행현황 │ 2026</t>
         </is>
@@ -8672,7 +8681,7 @@
       <c r="AQ1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="158" t="inlineStr">
+      <c r="A2" s="161" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 진행현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -8716,14 +8725,14 @@
       <c r="AL2" s="74" t="n"/>
       <c r="AM2" s="74" t="n"/>
       <c r="AN2" s="75" t="n"/>
-      <c r="AO2" s="159" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 14:34</t>
+      <c r="AO2" s="162" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 15:14</t>
         </is>
       </c>
       <c r="AP2" s="74" t="n"/>
       <c r="AQ2" s="75" t="n"/>
-      <c r="AU2" s="159" t="inlineStr">
+      <c r="AU2" s="162" t="inlineStr">
         <is>
           <t>업데이트: 2026-05-02 01:42</t>
         </is>
@@ -12585,7 +12594,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="157" t="inlineStr">
+      <c r="A1" s="160" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 출하현황 │ 2026</t>
         </is>
@@ -12614,7 +12623,7 @@
       <c r="W1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="158" t="inlineStr">
+      <c r="A2" s="161" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 출하현황  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -12638,9 +12647,9 @@
       <c r="R2" s="74" t="n"/>
       <c r="S2" s="74" t="n"/>
       <c r="T2" s="75" t="n"/>
-      <c r="U2" s="159" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 14:35</t>
+      <c r="U2" s="162" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 15:14</t>
         </is>
       </c>
       <c r="V2" s="74" t="n"/>
@@ -13691,7 +13700,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="157" t="inlineStr">
+      <c r="A1" s="160" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 완료이력 │ 2026</t>
         </is>
@@ -13727,7 +13736,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="158" t="inlineStr">
+      <c r="A2" s="161" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -13758,9 +13767,9 @@
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="75" t="n"/>
-      <c r="AB2" s="159" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 14:35</t>
+      <c r="AB2" s="162" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 15:14</t>
         </is>
       </c>
       <c r="AC2" s="74" t="n"/>
@@ -15730,7 +15739,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="157" t="inlineStr">
+      <c r="A1" s="160" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매핑조회(수주번호) │ 2026</t>
         </is>
@@ -15744,7 +15753,7 @@
       <c r="H1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="158" t="inlineStr">
+      <c r="A2" s="161" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 매핑조회  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -15753,9 +15762,9 @@
       <c r="C2" s="74" t="n"/>
       <c r="D2" s="74" t="n"/>
       <c r="E2" s="75" t="n"/>
-      <c r="F2" s="159" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 14:35</t>
+      <c r="F2" s="162" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 15:14</t>
         </is>
       </c>
       <c r="G2" s="74" t="n"/>
@@ -17377,7 +17386,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="157" t="inlineStr">
+      <c r="A1" s="160" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 관리코드발행대장 │ 2026</t>
         </is>
@@ -17390,7 +17399,7 @@
       <c r="G1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="158" t="inlineStr">
+      <c r="A2" s="161" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 관리코드발행  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -17398,9 +17407,9 @@
       <c r="B2" s="74" t="n"/>
       <c r="C2" s="74" t="n"/>
       <c r="D2" s="75" t="n"/>
-      <c r="E2" s="159" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 14:35</t>
+      <c r="E2" s="162" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 15:14</t>
         </is>
       </c>
       <c r="F2" s="74" t="n"/>
@@ -18586,7 +18595,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="157" t="inlineStr">
+      <c r="A1" s="160" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 수주번호생성대장 │ 2026</t>
         </is>
@@ -18598,16 +18607,16 @@
       <c r="F1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="158" t="inlineStr">
+      <c r="A2" s="161" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 수주번호생성  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
       </c>
       <c r="B2" s="74" t="n"/>
       <c r="C2" s="75" t="n"/>
-      <c r="D2" s="159" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 14:35</t>
+      <c r="D2" s="162" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 15:15</t>
         </is>
       </c>
       <c r="E2" s="74" t="n"/>
@@ -19662,7 +19671,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="157" t="inlineStr">
+      <c r="A1" s="160" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 매출마감 │ 2026</t>
         </is>
@@ -19698,7 +19707,7 @@
       <c r="AD1" s="75" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="158" t="inlineStr">
+      <c r="A2" s="161" t="inlineStr">
         <is>
           <t>㈜케이엔케이 자동화 PMS   │   💡 신규 수주 입력:  Ctrl+End (입력된 데이터 마지막 행 이동) → 다음 행에 입력 → 실행_PMS(영업·PM).bat 실행</t>
         </is>
@@ -19729,9 +19738,9 @@
       <c r="Y2" s="74" t="n"/>
       <c r="Z2" s="74" t="n"/>
       <c r="AA2" s="75" t="n"/>
-      <c r="AB2" s="159" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 14:35</t>
+      <c r="AB2" s="162" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 15:15</t>
         </is>
       </c>
       <c r="AC2" s="74" t="n"/>
